--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127697408</v>
+        <v>127698283</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481078</v>
+        <v>480987</v>
       </c>
       <c r="R2" t="n">
-        <v>6791705</v>
+        <v>6791630</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,60 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700590</v>
+        <v>127697277</v>
       </c>
       <c r="B3" t="n">
-        <v>92634</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481137</v>
+        <v>481009</v>
       </c>
       <c r="R3" t="n">
-        <v>6791517</v>
+        <v>6791717</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127698283</v>
+        <v>127697408</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480987</v>
+        <v>481078</v>
       </c>
       <c r="R4" t="n">
-        <v>6791630</v>
+        <v>6791705</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127697277</v>
+        <v>127698286</v>
       </c>
       <c r="B5" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481009</v>
+        <v>480923</v>
       </c>
       <c r="R5" t="n">
-        <v>6791717</v>
+        <v>6791625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127698286</v>
+        <v>127702760</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>79052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,42 +1124,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480923</v>
+        <v>481025</v>
       </c>
       <c r="R6" t="n">
-        <v>6791625</v>
+        <v>6791487</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,19 +1184,14 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:49</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,25 +1200,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127702760</v>
+        <v>127700382</v>
       </c>
       <c r="B7" t="n">
         <v>79052</v>
@@ -1249,19 +1248,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481025</v>
+        <v>481161</v>
       </c>
       <c r="R7" t="n">
-        <v>6791487</v>
+        <v>6791478</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1291,11 +1287,21 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>På gran</t>
@@ -1307,7 +1313,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1326,32 +1331,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700382</v>
+        <v>127700590</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>92634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,13 +1366,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481161</v>
+        <v>481137</v>
       </c>
       <c r="R8" t="n">
-        <v>6791478</v>
+        <v>6791517</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,12 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,12 +1426,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127698278</v>
+        <v>127697212</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,39 +3955,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480923</v>
+        <v>481033</v>
       </c>
       <c r="R32" t="n">
-        <v>6791625</v>
+        <v>6791734</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4024,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4049,14 +4044,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127697212</v>
+        <v>127699069</v>
       </c>
       <c r="B33" t="n">
         <v>79020</v>
@@ -4091,13 +4086,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481033</v>
+        <v>480958</v>
       </c>
       <c r="R33" t="n">
-        <v>6791734</v>
+        <v>6791568</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,7 +4131,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4156,14 +4151,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127699069</v>
+        <v>127697081</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -4194,17 +4189,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480958</v>
+        <v>481024</v>
       </c>
       <c r="R34" t="n">
-        <v>6791568</v>
+        <v>6791701</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4233,7 +4228,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4243,7 +4238,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4258,60 +4253,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127697081</v>
+        <v>127698467</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>91493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481024</v>
+        <v>480934</v>
       </c>
       <c r="R35" t="n">
-        <v>6791701</v>
+        <v>6791623</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4340,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4350,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,57 +4360,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127698467</v>
+        <v>127698278</v>
       </c>
       <c r="B36" t="n">
-        <v>91493</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480934</v>
+        <v>480923</v>
       </c>
       <c r="R36" t="n">
-        <v>6791623</v>
+        <v>6791625</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127698243</v>
+        <v>127701839</v>
       </c>
       <c r="B37" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,37 +4495,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480934</v>
+        <v>481051</v>
       </c>
       <c r="R37" t="n">
-        <v>6791648</v>
+        <v>6791546</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4554,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4564,7 +4567,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligr</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4573,6 +4581,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127701839</v>
+        <v>127698243</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,40 +4611,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481051</v>
+        <v>480934</v>
       </c>
       <c r="R38" t="n">
-        <v>6791546</v>
+        <v>6791648</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4664,7 +4670,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,12 +4680,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligr</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4688,7 +4689,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4707,48 +4707,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127698623</v>
+        <v>127698475</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>58033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480930</v>
+        <v>480971</v>
       </c>
       <c r="R39" t="n">
-        <v>6791596</v>
+        <v>6791584</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4777,7 +4782,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4787,7 +4792,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,62 +4807,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127698924</v>
+        <v>127700572</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480949</v>
+        <v>481155</v>
       </c>
       <c r="R40" t="n">
-        <v>6791564</v>
+        <v>6791512</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4914,65 +4914,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127698230</v>
+        <v>127700793</v>
       </c>
       <c r="B41" t="n">
-        <v>8439</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480934</v>
+        <v>481102</v>
       </c>
       <c r="R41" t="n">
-        <v>6791648</v>
+        <v>6791567</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5001,7 +4996,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5011,7 +5006,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5026,62 +5021,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127698475</v>
+        <v>127700334</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>79609</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480971</v>
+        <v>481204</v>
       </c>
       <c r="R42" t="n">
-        <v>6791584</v>
+        <v>6791461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5113,7 +5103,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5123,7 +5113,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5150,10 +5140,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127700334</v>
+        <v>127698623</v>
       </c>
       <c r="B43" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5161,37 +5151,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481204</v>
+        <v>480930</v>
       </c>
       <c r="R43" t="n">
-        <v>6791461</v>
+        <v>6791596</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5220,7 +5210,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5230,7 +5220,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5245,22 +5235,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Håkan Thenander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127698479</v>
+        <v>127698924</v>
       </c>
       <c r="B44" t="n">
-        <v>58340</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5268,39 +5258,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103044</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480971</v>
+        <v>480949</v>
       </c>
       <c r="R44" t="n">
-        <v>6791584</v>
+        <v>6791564</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,7 +5322,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5342,7 +5332,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5357,60 +5347,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127700572</v>
+        <v>127698230</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>8439</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481155</v>
+        <v>480934</v>
       </c>
       <c r="R45" t="n">
-        <v>6791512</v>
+        <v>6791648</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5439,7 +5434,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5449,7 +5444,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5464,57 +5459,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127700793</v>
+        <v>127698479</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>58340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481102</v>
+        <v>480971</v>
       </c>
       <c r="R46" t="n">
-        <v>6791567</v>
+        <v>6791584</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5802,45 +5802,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127697066</v>
+        <v>127698857</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480998</v>
+        <v>480934</v>
       </c>
       <c r="R49" t="n">
-        <v>6791729</v>
+        <v>6791542</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -5872,7 +5877,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5882,7 +5887,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5902,17 +5907,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127701141</v>
+        <v>127697743</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5920,37 +5925,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481104</v>
+        <v>481048</v>
       </c>
       <c r="R50" t="n">
-        <v>6791603</v>
+        <v>6791700</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5979,7 +5989,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5989,7 +5999,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6004,60 +6014,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127696761</v>
+        <v>127699193</v>
       </c>
       <c r="B51" t="n">
-        <v>79052</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480912</v>
+        <v>480980</v>
       </c>
       <c r="R51" t="n">
-        <v>6791695</v>
+        <v>6791570</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6086,7 +6101,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6096,7 +6111,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6116,57 +6131,52 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127698857</v>
+        <v>127696761</v>
       </c>
       <c r="B52" t="n">
-        <v>5177</v>
+        <v>79052</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480934</v>
+        <v>480912</v>
       </c>
       <c r="R52" t="n">
-        <v>6791542</v>
+        <v>6791695</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6198,7 +6208,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6208,7 +6218,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6228,17 +6238,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127697743</v>
+        <v>127697066</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6246,39 +6256,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481048</v>
+        <v>480998</v>
       </c>
       <c r="R53" t="n">
-        <v>6791700</v>
+        <v>6791729</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6310,7 +6315,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6320,7 +6325,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6340,7 +6345,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6566,50 +6571,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127699193</v>
+        <v>127701141</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480980</v>
+        <v>481104</v>
       </c>
       <c r="R56" t="n">
-        <v>6791570</v>
+        <v>6791603</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6666,22 +6666,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127698582</v>
+        <v>127700960</v>
       </c>
       <c r="B57" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6689,42 +6689,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480934</v>
+        <v>481132</v>
       </c>
       <c r="R57" t="n">
-        <v>6791623</v>
+        <v>6791620</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6753,7 +6748,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6763,7 +6758,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6778,12 +6773,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7023,10 +7018,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127697046</v>
+        <v>127698994</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>56855</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7034,27 +7029,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7063,10 +7058,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480998</v>
+        <v>480949</v>
       </c>
       <c r="R60" t="n">
-        <v>6791729</v>
+        <v>6791564</v>
       </c>
       <c r="S60" t="n">
         <v>9</v>
@@ -7098,7 +7093,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7108,7 +7103,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7128,60 +7123,55 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127699111</v>
+        <v>127697093</v>
       </c>
       <c r="B61" t="n">
-        <v>5197</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481041</v>
+        <v>481044</v>
       </c>
       <c r="R61" t="n">
-        <v>6791490</v>
+        <v>6791735</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7210,7 +7200,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7220,7 +7210,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7240,45 +7230,45 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127698670</v>
+        <v>127698582</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7287,10 +7277,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480930</v>
+        <v>480934</v>
       </c>
       <c r="R62" t="n">
-        <v>6791596</v>
+        <v>6791623</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7352,55 +7342,60 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127700960</v>
+        <v>127697046</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481132</v>
+        <v>480998</v>
       </c>
       <c r="R63" t="n">
-        <v>6791620</v>
+        <v>6791729</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7429,7 +7424,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7439,7 +7434,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7454,60 +7449,65 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127697093</v>
+        <v>127699111</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>5197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481044</v>
+        <v>481041</v>
       </c>
       <c r="R64" t="n">
-        <v>6791735</v>
+        <v>6791490</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127698994</v>
+        <v>127698670</v>
       </c>
       <c r="B65" t="n">
-        <v>56855</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7584,27 +7584,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7613,13 +7613,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480949</v>
+        <v>480930</v>
       </c>
       <c r="R65" t="n">
-        <v>6791564</v>
+        <v>6791596</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander, Håkan Thenander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127700777</v>
+        <v>127696956</v>
       </c>
       <c r="B82" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9463,37 +9463,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481102</v>
+        <v>480973</v>
       </c>
       <c r="R82" t="n">
-        <v>6791567</v>
+        <v>6791733</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9547,19 +9547,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127696956</v>
+        <v>127699017</v>
       </c>
       <c r="B83" t="n">
         <v>79020</v>
@@ -9594,13 +9594,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>480973</v>
+        <v>481001</v>
       </c>
       <c r="R83" t="n">
-        <v>6791733</v>
+        <v>6791490</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9659,17 +9659,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127699017</v>
+        <v>127700823</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9677,37 +9677,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481001</v>
+        <v>481147</v>
       </c>
       <c r="R84" t="n">
-        <v>6791490</v>
+        <v>6791569</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9736,7 +9741,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9746,7 +9751,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9773,10 +9778,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127700823</v>
+        <v>127699309</v>
       </c>
       <c r="B85" t="n">
-        <v>57660</v>
+        <v>78779</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9784,42 +9789,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481147</v>
+        <v>481074</v>
       </c>
       <c r="R85" t="n">
-        <v>6791569</v>
+        <v>6791631</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9873,22 +9873,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127699309</v>
+        <v>127699161</v>
       </c>
       <c r="B86" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9896,37 +9896,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481074</v>
+        <v>480980</v>
       </c>
       <c r="R86" t="n">
-        <v>6791631</v>
+        <v>6791570</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9980,60 +9980,69 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127699161</v>
+        <v>127700837</v>
       </c>
       <c r="B87" t="n">
-        <v>79609</v>
+        <v>56855</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>480980</v>
+        <v>481147</v>
       </c>
       <c r="R87" t="n">
-        <v>6791570</v>
+        <v>6791569</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10062,7 +10071,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10072,7 +10081,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10099,54 +10108,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700837</v>
+        <v>127700777</v>
       </c>
       <c r="B88" t="n">
-        <v>56855</v>
+        <v>79609</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481147</v>
+        <v>481102</v>
       </c>
       <c r="R88" t="n">
-        <v>6791569</v>
+        <v>6791567</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10203,12 +10203,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10643,10 +10643,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127699200</v>
+        <v>127699307</v>
       </c>
       <c r="B93" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10654,42 +10654,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480980</v>
+        <v>481074</v>
       </c>
       <c r="R93" t="n">
-        <v>6791570</v>
+        <v>6791631</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10718,7 +10713,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10728,7 +10723,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10743,22 +10738,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127699307</v>
+        <v>127699026</v>
       </c>
       <c r="B94" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10766,21 +10761,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10790,10 +10785,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481074</v>
+        <v>481040</v>
       </c>
       <c r="R94" t="n">
-        <v>6791631</v>
+        <v>6791597</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10862,7 +10857,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127699026</v>
+        <v>127696785</v>
       </c>
       <c r="B95" t="n">
         <v>79020</v>
@@ -10897,10 +10892,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481040</v>
+        <v>480937</v>
       </c>
       <c r="R95" t="n">
-        <v>6791597</v>
+        <v>6791705</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10969,7 +10964,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127696785</v>
+        <v>127697854</v>
       </c>
       <c r="B96" t="n">
         <v>79020</v>
@@ -11004,13 +10999,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>480937</v>
+        <v>481035</v>
       </c>
       <c r="R96" t="n">
-        <v>6791705</v>
+        <v>6791695</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11076,10 +11071,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127697854</v>
+        <v>127699200</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11087,37 +11082,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481035</v>
+        <v>480980</v>
       </c>
       <c r="R97" t="n">
-        <v>6791695</v>
+        <v>6791570</v>
       </c>
       <c r="S97" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11171,12 +11171,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -13051,48 +13051,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127697443</v>
+        <v>127697402</v>
       </c>
       <c r="B115" t="n">
-        <v>79020</v>
+        <v>92626</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>481071</v>
+        <v>481078</v>
       </c>
       <c r="R115" t="n">
-        <v>6791709</v>
+        <v>6791705</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13146,44 +13146,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127697101</v>
+        <v>127697747</v>
       </c>
       <c r="B116" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13193,10 +13193,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>481033</v>
+        <v>481048</v>
       </c>
       <c r="R116" t="n">
-        <v>6791742</v>
+        <v>6791700</v>
       </c>
       <c r="S116" t="n">
         <v>9</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13238,7 +13238,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Betade tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13258,55 +13263,60 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127699444</v>
+        <v>127699098</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>5177</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>481127</v>
+        <v>481041</v>
       </c>
       <c r="R117" t="n">
-        <v>6791446</v>
+        <v>6791490</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13335,7 +13345,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13345,7 +13355,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13372,48 +13382,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127697402</v>
+        <v>127699090</v>
       </c>
       <c r="B118" t="n">
-        <v>92626</v>
+        <v>57663</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>481078</v>
+        <v>480970</v>
       </c>
       <c r="R118" t="n">
-        <v>6791705</v>
+        <v>6791562</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13442,7 +13457,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13452,7 +13467,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13479,48 +13494,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127697747</v>
+        <v>127697443</v>
       </c>
       <c r="B119" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>481048</v>
+        <v>481071</v>
       </c>
       <c r="R119" t="n">
-        <v>6791700</v>
+        <v>6791709</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13549,7 +13564,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13559,12 +13574,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Betade tall</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13579,65 +13589,60 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127699098</v>
+        <v>127697101</v>
       </c>
       <c r="B120" t="n">
-        <v>5177</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>481041</v>
+        <v>481033</v>
       </c>
       <c r="R120" t="n">
-        <v>6791490</v>
+        <v>6791742</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13666,7 +13671,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13676,7 +13681,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13696,17 +13701,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127699090</v>
+        <v>127699444</v>
       </c>
       <c r="B121" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13714,39 +13719,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>480970</v>
+        <v>481127</v>
       </c>
       <c r="R121" t="n">
-        <v>6791562</v>
+        <v>6791446</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13815,10 +13815,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127700636</v>
+        <v>127699075</v>
       </c>
       <c r="B122" t="n">
-        <v>79052</v>
+        <v>57823</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13826,37 +13826,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>481117</v>
+        <v>480958</v>
       </c>
       <c r="R122" t="n">
-        <v>6791518</v>
+        <v>6791568</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13885,7 +13890,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13895,7 +13900,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13922,10 +13927,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127699075</v>
+        <v>127700636</v>
       </c>
       <c r="B123" t="n">
-        <v>57823</v>
+        <v>79052</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13933,42 +13938,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480958</v>
+        <v>481117</v>
       </c>
       <c r="R123" t="n">
-        <v>6791568</v>
+        <v>6791518</v>
       </c>
       <c r="S123" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14034,7 +14034,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127702746</v>
+        <v>127697104</v>
       </c>
       <c r="B124" t="n">
         <v>79052</v>
@@ -14063,22 +14063,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>481027</v>
+        <v>481033</v>
       </c>
       <c r="R124" t="n">
-        <v>6791478</v>
+        <v>6791742</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14105,14 +14102,19 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14121,26 +14123,25 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127702694</v>
+        <v>127697268</v>
       </c>
       <c r="B125" t="n">
         <v>79052</v>
@@ -14169,19 +14170,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>480974</v>
+        <v>480976</v>
       </c>
       <c r="R125" t="n">
-        <v>6791516</v>
+        <v>6791656</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14211,11 +14209,21 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
       <c r="AC125" t="inlineStr">
         <is>
           <t>På gran</t>
@@ -14227,7 +14235,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14246,10 +14253,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127697104</v>
+        <v>127698802</v>
       </c>
       <c r="B126" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14257,34 +14264,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>481033</v>
+        <v>481014</v>
       </c>
       <c r="R126" t="n">
-        <v>6791742</v>
+        <v>6791631</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14316,7 +14323,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14326,7 +14333,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14341,22 +14348,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127697268</v>
+        <v>127697283</v>
       </c>
       <c r="B127" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14364,37 +14371,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>480976</v>
+        <v>481009</v>
       </c>
       <c r="R127" t="n">
-        <v>6791656</v>
+        <v>6791717</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14423,7 +14430,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14433,12 +14440,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14453,22 +14455,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127698802</v>
+        <v>127699527</v>
       </c>
       <c r="B128" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14476,34 +14478,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>481014</v>
+        <v>481147</v>
       </c>
       <c r="R128" t="n">
-        <v>6791631</v>
+        <v>6791614</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14572,48 +14579,53 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127697283</v>
+        <v>127698996</v>
       </c>
       <c r="B129" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>481009</v>
+        <v>480951</v>
       </c>
       <c r="R129" t="n">
-        <v>6791717</v>
+        <v>6791482</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14642,7 +14654,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14652,7 +14664,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14667,22 +14679,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127699527</v>
+        <v>127702746</v>
       </c>
       <c r="B130" t="n">
-        <v>57660</v>
+        <v>79052</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14690,42 +14702,40 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>481147</v>
+        <v>481027</v>
       </c>
       <c r="R130" t="n">
-        <v>6791614</v>
+        <v>6791478</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14752,19 +14762,14 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>09:34</t>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14773,71 +14778,70 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127698996</v>
+        <v>127702694</v>
       </c>
       <c r="B131" t="n">
-        <v>56855</v>
+        <v>79052</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480951</v>
+        <v>480974</v>
       </c>
       <c r="R131" t="n">
-        <v>6791482</v>
+        <v>6791516</v>
       </c>
       <c r="S131" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14864,19 +14868,14 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:52</t>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14885,18 +14884,19 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -17404,10 +17404,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127698346</v>
+        <v>127698885</v>
       </c>
       <c r="B155" t="n">
-        <v>57660</v>
+        <v>57823</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17415,39 +17415,43 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>480971</v>
+        <v>480932</v>
       </c>
       <c r="R155" t="n">
-        <v>6791584</v>
+        <v>6791598</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17479,7 +17483,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17489,7 +17493,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17504,57 +17508,57 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127698037</v>
+        <v>127699451</v>
       </c>
       <c r="B156" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>480992</v>
+        <v>481157</v>
       </c>
       <c r="R156" t="n">
-        <v>6791667</v>
+        <v>6791437</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17586,7 +17590,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17596,7 +17600,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17611,22 +17615,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127698374</v>
+        <v>127699297</v>
       </c>
       <c r="B157" t="n">
-        <v>57663</v>
+        <v>79609</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17634,42 +17638,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480934</v>
+        <v>481074</v>
       </c>
       <c r="R157" t="n">
-        <v>6791623</v>
+        <v>6791631</v>
       </c>
       <c r="S157" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17698,7 +17697,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17708,7 +17707,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17723,65 +17722,65 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127699095</v>
+        <v>127698346</v>
       </c>
       <c r="B158" t="n">
-        <v>5177</v>
+        <v>57660</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>480970</v>
+        <v>480971</v>
       </c>
       <c r="R158" t="n">
-        <v>6791562</v>
+        <v>6791584</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17810,7 +17809,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17820,7 +17819,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17835,22 +17834,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127698885</v>
+        <v>127698037</v>
       </c>
       <c r="B159" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17858,43 +17857,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>480932</v>
+        <v>480992</v>
       </c>
       <c r="R159" t="n">
-        <v>6791598</v>
+        <v>6791667</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17926,7 +17916,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17936,7 +17926,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17951,60 +17941,65 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127699451</v>
+        <v>127698374</v>
       </c>
       <c r="B160" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>481157</v>
+        <v>480934</v>
       </c>
       <c r="R160" t="n">
-        <v>6791437</v>
+        <v>6791623</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18033,7 +18028,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18043,7 +18038,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18070,48 +18065,53 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127699297</v>
+        <v>127699095</v>
       </c>
       <c r="B161" t="n">
-        <v>79609</v>
+        <v>5177</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>481074</v>
+        <v>480970</v>
       </c>
       <c r="R161" t="n">
-        <v>6791631</v>
+        <v>6791562</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18165,12 +18165,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127698286</v>
+        <v>127702760</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>79061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480923</v>
+        <v>481025</v>
       </c>
       <c r="R2" t="n">
-        <v>6791625</v>
+        <v>6791487</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +746,14 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:49</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127697277</v>
+        <v>127700382</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481009</v>
+        <v>481161</v>
       </c>
       <c r="R3" t="n">
-        <v>6791717</v>
+        <v>6791478</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +861,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,60 +881,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127698283</v>
+        <v>127700590</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480987</v>
+        <v>481137</v>
       </c>
       <c r="R4" t="n">
-        <v>6791630</v>
+        <v>6791517</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,19 +988,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127697408</v>
+        <v>127701512</v>
       </c>
       <c r="B5" t="n">
         <v>57672</v>
@@ -1032,7 +1031,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1041,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481078</v>
+        <v>481100</v>
       </c>
       <c r="R5" t="n">
-        <v>6791705</v>
+        <v>6791578</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1076,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127702760</v>
+        <v>127697277</v>
       </c>
       <c r="B6" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,40 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481025</v>
+        <v>481009</v>
       </c>
       <c r="R6" t="n">
-        <v>6791487</v>
+        <v>6791717</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,14 +1180,19 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,29 +1201,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700382</v>
+        <v>127698283</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481161</v>
+        <v>480987</v>
       </c>
       <c r="R7" t="n">
-        <v>6791478</v>
+        <v>6791630</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,12 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,60 +1314,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700590</v>
+        <v>127698286</v>
       </c>
       <c r="B8" t="n">
-        <v>92654</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481137</v>
+        <v>480923</v>
       </c>
       <c r="R8" t="n">
-        <v>6791517</v>
+        <v>6791625</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127701512</v>
+        <v>127697408</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1469,7 +1469,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481100</v>
+        <v>481078</v>
       </c>
       <c r="R9" t="n">
-        <v>6791578</v>
+        <v>6791705</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127698067</v>
+        <v>127701188</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480997</v>
+        <v>481073</v>
       </c>
       <c r="R16" t="n">
-        <v>6791673</v>
+        <v>6791616</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2267,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2282,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2309,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127697100</v>
+        <v>127698067</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2335,17 +2340,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481032</v>
+        <v>480997</v>
       </c>
       <c r="R17" t="n">
-        <v>6791729</v>
+        <v>6791673</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2374,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,19 +2404,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127697311</v>
+        <v>127697100</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2442,17 +2447,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481070</v>
+        <v>481032</v>
       </c>
       <c r="R18" t="n">
-        <v>6791717</v>
+        <v>6791729</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2496,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,19 +2511,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127698861</v>
+        <v>127697311</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2549,17 +2554,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481024</v>
+        <v>481070</v>
       </c>
       <c r="R19" t="n">
-        <v>6791620</v>
+        <v>6791717</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2603,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,22 +2618,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127699269</v>
+        <v>127698861</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,39 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481074</v>
+        <v>481024</v>
       </c>
       <c r="R20" t="n">
-        <v>6791631</v>
+        <v>6791620</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127698539</v>
+        <v>127699033</v>
       </c>
       <c r="B21" t="n">
         <v>5177</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480934</v>
+        <v>480958</v>
       </c>
       <c r="R21" t="n">
-        <v>6791623</v>
+        <v>6791568</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,53 +2849,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127699033</v>
+        <v>127699269</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480958</v>
+        <v>481074</v>
       </c>
       <c r="R22" t="n">
-        <v>6791568</v>
+        <v>6791631</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,12 +2949,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3068,38 +3068,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127701188</v>
+        <v>127698539</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481073</v>
+        <v>480934</v>
       </c>
       <c r="R24" t="n">
-        <v>6791616</v>
+        <v>6791623</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127698896</v>
+        <v>127697758</v>
       </c>
       <c r="B25" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,37 +3191,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480939</v>
+        <v>481047</v>
       </c>
       <c r="R25" t="n">
-        <v>6791551</v>
+        <v>6791700</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,19 +3275,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127697758</v>
+        <v>127699426</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481047</v>
+        <v>481074</v>
       </c>
       <c r="R26" t="n">
-        <v>6791700</v>
+        <v>6791631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127699426</v>
+        <v>127701320</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,37 +3405,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481074</v>
+        <v>481015</v>
       </c>
       <c r="R27" t="n">
-        <v>6791631</v>
+        <v>6791581</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3474,7 +3474,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,60 +3494,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127701320</v>
+        <v>127701326</v>
       </c>
       <c r="B28" t="n">
-        <v>79061</v>
+        <v>5177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481015</v>
+        <v>481100</v>
       </c>
       <c r="R28" t="n">
-        <v>6791581</v>
+        <v>6791578</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3571,7 +3581,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3581,12 +3591,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,65 +3606,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127701326</v>
+        <v>127698896</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>79061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481100</v>
+        <v>480939</v>
       </c>
       <c r="R29" t="n">
-        <v>6791578</v>
+        <v>6791551</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127698467</v>
+        <v>127697912</v>
       </c>
       <c r="B31" t="n">
-        <v>91513</v>
+        <v>79061</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480934</v>
+        <v>481035</v>
       </c>
       <c r="R31" t="n">
-        <v>6791623</v>
+        <v>6791685</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3912,7 +3912,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,44 +3932,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127697912</v>
+        <v>127698467</v>
       </c>
       <c r="B32" t="n">
-        <v>79061</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3974,13 +3979,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481035</v>
+        <v>480934</v>
       </c>
       <c r="R32" t="n">
-        <v>6791685</v>
+        <v>6791623</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4009,7 +4014,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4019,12 +4024,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,19 +4039,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127699069</v>
+        <v>127697212</v>
       </c>
       <c r="B33" t="n">
         <v>79029</v>
@@ -4086,13 +4086,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480958</v>
+        <v>481033</v>
       </c>
       <c r="R33" t="n">
-        <v>6791568</v>
+        <v>6791734</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127697081</v>
+        <v>127699069</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -4189,17 +4189,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481024</v>
+        <v>480958</v>
       </c>
       <c r="R34" t="n">
-        <v>6791701</v>
+        <v>6791568</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,19 +4253,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127697212</v>
+        <v>127697081</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4296,17 +4296,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481033</v>
+        <v>481024</v>
       </c>
       <c r="R35" t="n">
-        <v>6791734</v>
+        <v>6791701</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4707,45 +4707,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127700334</v>
+        <v>127698479</v>
       </c>
       <c r="B39" t="n">
-        <v>79618</v>
+        <v>58349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481204</v>
+        <v>480971</v>
       </c>
       <c r="R39" t="n">
-        <v>6791461</v>
+        <v>6791584</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4777,7 +4782,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4787,7 +4792,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4814,10 +4819,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127698623</v>
+        <v>127699014</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,37 +4830,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480930</v>
+        <v>481040</v>
       </c>
       <c r="R40" t="n">
-        <v>6791596</v>
+        <v>6791597</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4884,7 +4889,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4894,7 +4899,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4909,65 +4914,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127698479</v>
+        <v>127698623</v>
       </c>
       <c r="B41" t="n">
-        <v>58349</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480971</v>
+        <v>480930</v>
       </c>
       <c r="R41" t="n">
-        <v>6791584</v>
+        <v>6791596</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5021,57 +5021,62 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127700572</v>
+        <v>127698475</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481155</v>
+        <v>480971</v>
       </c>
       <c r="R42" t="n">
-        <v>6791512</v>
+        <v>6791584</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5103,7 +5108,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5113,7 +5118,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,45 +5145,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127700793</v>
+        <v>127698924</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481102</v>
+        <v>480949</v>
       </c>
       <c r="R43" t="n">
-        <v>6791567</v>
+        <v>6791564</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5210,7 +5220,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5220,7 +5230,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5235,22 +5245,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127698475</v>
+        <v>127698230</v>
       </c>
       <c r="B44" t="n">
-        <v>58042</v>
+        <v>8439</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5258,42 +5268,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480971</v>
+        <v>480934</v>
       </c>
       <c r="R44" t="n">
-        <v>6791584</v>
+        <v>6791648</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5322,7 +5332,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5332,7 +5342,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5347,22 +5357,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127698924</v>
+        <v>127701600</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5370,42 +5380,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480949</v>
+        <v>481051</v>
       </c>
       <c r="R45" t="n">
-        <v>6791564</v>
+        <v>6791546</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5434,7 +5439,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5444,7 +5449,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5471,53 +5481,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127698230</v>
+        <v>127700572</v>
       </c>
       <c r="B46" t="n">
-        <v>8439</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480934</v>
+        <v>481155</v>
       </c>
       <c r="R46" t="n">
-        <v>6791648</v>
+        <v>6791512</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5546,7 +5551,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5556,7 +5561,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5571,22 +5576,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127699014</v>
+        <v>127700793</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,21 +5599,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5618,10 +5623,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481040</v>
+        <v>481102</v>
       </c>
       <c r="R47" t="n">
-        <v>6791597</v>
+        <v>6791567</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5653,7 +5658,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5663,7 +5668,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5690,48 +5695,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127701600</v>
+        <v>127700334</v>
       </c>
       <c r="B48" t="n">
-        <v>56864</v>
+        <v>79618</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481051</v>
+        <v>481204</v>
       </c>
       <c r="R48" t="n">
-        <v>6791546</v>
+        <v>6791461</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5760,7 +5765,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5770,12 +5775,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,12 +5790,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6897,47 +6897,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127696742</v>
+        <v>127699410</v>
       </c>
       <c r="B59" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6946,10 +6937,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480917</v>
+        <v>481141</v>
       </c>
       <c r="R59" t="n">
-        <v>6791694</v>
+        <v>6791461</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6981,7 +6972,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6991,7 +6982,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7018,53 +7009,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127698994</v>
+        <v>127700960</v>
       </c>
       <c r="B60" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480949</v>
+        <v>481132</v>
       </c>
       <c r="R60" t="n">
-        <v>6791564</v>
+        <v>6791620</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7093,7 +7079,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7103,7 +7089,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7118,50 +7104,59 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127699410</v>
+        <v>127696742</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7170,10 +7165,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481141</v>
+        <v>480917</v>
       </c>
       <c r="R61" t="n">
-        <v>6791461</v>
+        <v>6791694</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7205,7 +7200,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7215,7 +7210,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7242,10 +7237,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127697046</v>
+        <v>127698994</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7253,27 +7248,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7282,10 +7277,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480998</v>
+        <v>480949</v>
       </c>
       <c r="R62" t="n">
-        <v>6791729</v>
+        <v>6791564</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7317,7 +7312,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7327,7 +7322,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7347,17 +7342,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127699111</v>
+        <v>127697046</v>
       </c>
       <c r="B63" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7365,21 +7360,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7394,13 +7389,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481041</v>
+        <v>480998</v>
       </c>
       <c r="R63" t="n">
-        <v>6791490</v>
+        <v>6791729</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7429,7 +7424,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7439,7 +7434,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7459,17 +7454,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127698670</v>
+        <v>127699111</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7477,21 +7472,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7506,13 +7501,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480930</v>
+        <v>481041</v>
       </c>
       <c r="R64" t="n">
-        <v>6791596</v>
+        <v>6791490</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7541,7 +7536,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7551,7 +7546,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7578,48 +7573,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127700960</v>
+        <v>127698670</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481132</v>
+        <v>480930</v>
       </c>
       <c r="R65" t="n">
-        <v>6791620</v>
+        <v>6791596</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7673,12 +7673,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127698916</v>
+        <v>127698978</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7808,37 +7808,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480963</v>
+        <v>480949</v>
       </c>
       <c r="R67" t="n">
-        <v>6791579</v>
+        <v>6791564</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7867,7 +7872,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7877,12 +7882,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På en gammal tallstubbe</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7897,60 +7897,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127697134</v>
+        <v>127697874</v>
       </c>
       <c r="B68" t="n">
-        <v>79061</v>
+        <v>58042</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480998</v>
+        <v>481017</v>
       </c>
       <c r="R68" t="n">
-        <v>6791743</v>
+        <v>6791670</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7979,7 +7984,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7989,12 +7994,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8009,22 +8009,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127697245</v>
+        <v>127699211</v>
       </c>
       <c r="B69" t="n">
-        <v>91317</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8032,37 +8032,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481040</v>
+        <v>481084</v>
       </c>
       <c r="R69" t="n">
-        <v>6791735</v>
+        <v>6791483</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8091,7 +8096,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8101,7 +8106,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8121,17 +8126,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127698383</v>
+        <v>127699004</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8139,37 +8144,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480934</v>
+        <v>481040</v>
       </c>
       <c r="R70" t="n">
-        <v>6791623</v>
+        <v>6791597</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8198,7 +8203,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8208,7 +8213,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8223,60 +8228,65 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127697142</v>
+        <v>127699166</v>
       </c>
       <c r="B71" t="n">
-        <v>79647</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481015</v>
+        <v>480980</v>
       </c>
       <c r="R71" t="n">
-        <v>6791712</v>
+        <v>6791570</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8305,7 +8315,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8315,7 +8325,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8330,57 +8340,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127698146</v>
+        <v>127697024</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480960</v>
+        <v>480998</v>
       </c>
       <c r="R72" t="n">
-        <v>6791643</v>
+        <v>6791729</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8412,7 +8427,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8422,7 +8437,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Tjädertall välbetad</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8437,57 +8457,62 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127699151</v>
+        <v>127698878</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480980</v>
+        <v>480932</v>
       </c>
       <c r="R73" t="n">
-        <v>6791570</v>
+        <v>6791598</v>
       </c>
       <c r="S73" t="n">
         <v>9</v>
@@ -8519,7 +8544,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,7 +8554,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8556,10 +8581,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127698242</v>
+        <v>127698916</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8567,37 +8592,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480945</v>
+        <v>480963</v>
       </c>
       <c r="R74" t="n">
-        <v>6791620</v>
+        <v>6791579</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8626,7 +8651,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8636,12 +8661,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>På en gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8656,65 +8681,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127699166</v>
+        <v>127697134</v>
       </c>
       <c r="B75" t="n">
-        <v>5177</v>
+        <v>79061</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480980</v>
+        <v>480998</v>
       </c>
       <c r="R75" t="n">
-        <v>6791570</v>
+        <v>6791743</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8743,7 +8763,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8753,7 +8773,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8768,22 +8793,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127697024</v>
+        <v>127697245</v>
       </c>
       <c r="B76" t="n">
-        <v>56864</v>
+        <v>91317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8791,39 +8816,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>480998</v>
+        <v>481040</v>
       </c>
       <c r="R76" t="n">
-        <v>6791729</v>
+        <v>6791735</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8866,11 +8886,6 @@
       <c r="AB76" t="inlineStr">
         <is>
           <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Tjädertall välbetad</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8897,50 +8912,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127698878</v>
+        <v>127698383</v>
       </c>
       <c r="B77" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480932</v>
+        <v>480934</v>
       </c>
       <c r="R77" t="n">
-        <v>6791598</v>
+        <v>6791623</v>
       </c>
       <c r="S77" t="n">
         <v>9</v>
@@ -8972,7 +8982,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8982,7 +8992,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9009,10 +9019,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127698978</v>
+        <v>127697142</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9020,39 +9030,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480949</v>
+        <v>481015</v>
       </c>
       <c r="R78" t="n">
-        <v>6791564</v>
+        <v>6791712</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9084,7 +9089,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9094,7 +9099,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9109,65 +9114,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127697874</v>
+        <v>127698146</v>
       </c>
       <c r="B79" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481017</v>
+        <v>480960</v>
       </c>
       <c r="R79" t="n">
-        <v>6791670</v>
+        <v>6791643</v>
       </c>
       <c r="S79" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9233,10 +9233,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127699004</v>
+        <v>127699151</v>
       </c>
       <c r="B80" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9244,37 +9244,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481040</v>
+        <v>480980</v>
       </c>
       <c r="R80" t="n">
-        <v>6791597</v>
+        <v>6791570</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9328,65 +9328,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127699211</v>
+        <v>127698242</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481084</v>
+        <v>480945</v>
       </c>
       <c r="R81" t="n">
-        <v>6791483</v>
+        <v>6791620</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9415,7 +9410,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9425,7 +9420,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9440,22 +9440,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127699017</v>
+        <v>127699161</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9463,21 +9463,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481001</v>
+        <v>480980</v>
       </c>
       <c r="R82" t="n">
-        <v>6791490</v>
+        <v>6791570</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9559,10 +9559,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127700777</v>
+        <v>127699309</v>
       </c>
       <c r="B83" t="n">
-        <v>79618</v>
+        <v>78788</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9570,21 +9570,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481102</v>
+        <v>481074</v>
       </c>
       <c r="R83" t="n">
-        <v>6791567</v>
+        <v>6791631</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9666,32 +9666,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127699161</v>
+        <v>127700910</v>
       </c>
       <c r="B84" t="n">
-        <v>79618</v>
+        <v>92642</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9701,13 +9701,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480980</v>
+        <v>481139</v>
       </c>
       <c r="R84" t="n">
-        <v>6791570</v>
+        <v>6791575</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9773,45 +9773,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127699309</v>
+        <v>127700837</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>56864</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481074</v>
+        <v>481147</v>
       </c>
       <c r="R85" t="n">
-        <v>6791631</v>
+        <v>6791569</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9843,7 +9852,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9853,7 +9862,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9868,22 +9877,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127700371</v>
+        <v>127700777</v>
       </c>
       <c r="B86" t="n">
-        <v>91352</v>
+        <v>79618</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9891,34 +9900,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481171</v>
+        <v>481102</v>
       </c>
       <c r="R86" t="n">
-        <v>6791459</v>
+        <v>6791567</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9950,7 +9959,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9960,7 +9969,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9975,19 +9984,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127700455</v>
+        <v>127699017</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -10018,14 +10027,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481162</v>
+        <v>481001</v>
       </c>
       <c r="R87" t="n">
-        <v>6791491</v>
+        <v>6791490</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10057,7 +10066,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10076,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10082,12 +10091,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10201,32 +10210,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127700910</v>
+        <v>127700371</v>
       </c>
       <c r="B89" t="n">
-        <v>92642</v>
+        <v>91352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10236,10 +10245,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481139</v>
+        <v>481171</v>
       </c>
       <c r="R89" t="n">
-        <v>6791575</v>
+        <v>6791459</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10308,10 +10317,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127700497</v>
+        <v>127700455</v>
       </c>
       <c r="B90" t="n">
-        <v>75153</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,21 +10328,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10343,10 +10352,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481155</v>
+        <v>481162</v>
       </c>
       <c r="R90" t="n">
-        <v>6791512</v>
+        <v>6791491</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10415,10 +10424,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127700823</v>
+        <v>127700497</v>
       </c>
       <c r="B91" t="n">
-        <v>57669</v>
+        <v>75153</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10426,42 +10435,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481147</v>
+        <v>481155</v>
       </c>
       <c r="R91" t="n">
-        <v>6791569</v>
+        <v>6791512</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10490,7 +10494,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10500,7 +10504,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10515,54 +10519,50 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127700837</v>
+        <v>127700823</v>
       </c>
       <c r="B92" t="n">
-        <v>56864</v>
+        <v>57669</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10577,7 +10577,7 @@
         <v>6791569</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10643,45 +10643,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127699374</v>
+        <v>127698937</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481074</v>
+        <v>480949</v>
       </c>
       <c r="R93" t="n">
-        <v>6791631</v>
+        <v>6791564</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10738,22 +10738,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127698937</v>
+        <v>127699026</v>
       </c>
       <c r="B94" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10761,34 +10761,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480949</v>
+        <v>481040</v>
       </c>
       <c r="R94" t="n">
-        <v>6791564</v>
+        <v>6791597</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10845,22 +10845,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127697267</v>
+        <v>127696785</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10868,42 +10868,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481070</v>
+        <v>480937</v>
       </c>
       <c r="R95" t="n">
-        <v>6791717</v>
+        <v>6791705</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10932,7 +10927,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10942,7 +10937,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10957,65 +10952,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127697901</v>
+        <v>127697854</v>
       </c>
       <c r="B96" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481006</v>
+        <v>481035</v>
       </c>
       <c r="R96" t="n">
-        <v>6791673</v>
+        <v>6791695</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11044,7 +11034,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11054,7 +11044,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11069,22 +11059,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127699307</v>
+        <v>127697267</v>
       </c>
       <c r="B97" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11092,37 +11082,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481074</v>
+        <v>481070</v>
       </c>
       <c r="R97" t="n">
-        <v>6791631</v>
+        <v>6791717</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11151,7 +11146,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11161,7 +11156,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11176,50 +11171,50 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127699200</v>
+        <v>127697901</v>
       </c>
       <c r="B98" t="n">
-        <v>57669</v>
+        <v>56864</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11228,10 +11223,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480980</v>
+        <v>481006</v>
       </c>
       <c r="R98" t="n">
-        <v>6791570</v>
+        <v>6791673</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -11263,7 +11258,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11273,7 +11268,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11300,32 +11295,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127699026</v>
+        <v>127699374</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11335,10 +11330,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481040</v>
+        <v>481074</v>
       </c>
       <c r="R99" t="n">
-        <v>6791597</v>
+        <v>6791631</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11407,10 +11402,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127696785</v>
+        <v>127699307</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11418,21 +11413,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11442,10 +11437,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480937</v>
+        <v>481074</v>
       </c>
       <c r="R100" t="n">
-        <v>6791705</v>
+        <v>6791631</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11514,10 +11509,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127697854</v>
+        <v>127699200</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11525,37 +11520,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>481035</v>
+        <v>480980</v>
       </c>
       <c r="R101" t="n">
-        <v>6791695</v>
+        <v>6791570</v>
       </c>
       <c r="S101" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11609,12 +11609,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11961,32 +11961,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127697059</v>
+        <v>127699081</v>
       </c>
       <c r="B105" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11996,13 +11996,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480998</v>
+        <v>480958</v>
       </c>
       <c r="R105" t="n">
-        <v>6791729</v>
+        <v>6791568</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12061,39 +12061,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127699081</v>
+        <v>127697411</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480958</v>
+        <v>481081</v>
       </c>
       <c r="R106" t="n">
-        <v>6791568</v>
+        <v>6791711</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12148,7 +12148,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På roten av en gammal tallåga</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12163,44 +12168,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127697411</v>
+        <v>127701548</v>
       </c>
       <c r="B107" t="n">
-        <v>79618</v>
+        <v>91317</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12210,13 +12215,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>481081</v>
+        <v>481100</v>
       </c>
       <c r="R107" t="n">
-        <v>6791711</v>
+        <v>6791578</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12245,7 +12250,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12255,12 +12260,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>På roten av en gammal tallåga</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12275,44 +12275,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127701548</v>
+        <v>127697059</v>
       </c>
       <c r="B108" t="n">
-        <v>91317</v>
+        <v>79061</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12322,13 +12322,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>481100</v>
+        <v>480998</v>
       </c>
       <c r="R108" t="n">
-        <v>6791578</v>
+        <v>6791729</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12387,52 +12387,57 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127696731</v>
+        <v>127701318</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480916</v>
+        <v>481100</v>
       </c>
       <c r="R109" t="n">
-        <v>6791696</v>
+        <v>6791578</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12464,7 +12469,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12474,7 +12479,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12489,22 +12494,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127698216</v>
+        <v>127698632</v>
       </c>
       <c r="B110" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12512,37 +12517,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480972</v>
+        <v>480963</v>
       </c>
       <c r="R110" t="n">
-        <v>6791653</v>
+        <v>6791579</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12571,7 +12581,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12581,7 +12591,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12596,39 +12606,39 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127698632</v>
+        <v>127698322</v>
       </c>
       <c r="B111" t="n">
-        <v>57672</v>
+        <v>5197</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12637,24 +12647,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480963</v>
+        <v>480936</v>
       </c>
       <c r="R111" t="n">
-        <v>6791579</v>
+        <v>6791610</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12683,7 +12688,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12693,7 +12698,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12708,12 +12713,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12832,48 +12837,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127698322</v>
+        <v>127696731</v>
       </c>
       <c r="B113" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480936</v>
+        <v>480916</v>
       </c>
       <c r="R113" t="n">
-        <v>6791610</v>
+        <v>6791696</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12902,7 +12907,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12912,7 +12917,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12927,65 +12932,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127701318</v>
+        <v>127698216</v>
       </c>
       <c r="B114" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>481100</v>
+        <v>480972</v>
       </c>
       <c r="R114" t="n">
-        <v>6791578</v>
+        <v>6791653</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13051,10 +13051,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127697443</v>
+        <v>127700636</v>
       </c>
       <c r="B115" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13062,37 +13062,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>481071</v>
+        <v>481117</v>
       </c>
       <c r="R115" t="n">
-        <v>6791709</v>
+        <v>6791518</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13146,19 +13146,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127699444</v>
+        <v>127697443</v>
       </c>
       <c r="B116" t="n">
         <v>79029</v>
@@ -13189,14 +13189,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>481127</v>
+        <v>481071</v>
       </c>
       <c r="R116" t="n">
-        <v>6791446</v>
+        <v>6791709</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13253,22 +13253,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127699090</v>
+        <v>127699444</v>
       </c>
       <c r="B117" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13276,39 +13276,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>480970</v>
+        <v>481127</v>
       </c>
       <c r="R117" t="n">
-        <v>6791562</v>
+        <v>6791446</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13340,7 +13335,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13350,7 +13345,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13377,53 +13372,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127699075</v>
+        <v>127697402</v>
       </c>
       <c r="B118" t="n">
-        <v>57832</v>
+        <v>92646</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>480958</v>
+        <v>481078</v>
       </c>
       <c r="R118" t="n">
-        <v>6791568</v>
+        <v>6791705</v>
       </c>
       <c r="S118" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13452,7 +13442,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13462,7 +13452,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13489,32 +13479,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127697402</v>
+        <v>127697101</v>
       </c>
       <c r="B119" t="n">
-        <v>92646</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13524,10 +13514,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>481078</v>
+        <v>481033</v>
       </c>
       <c r="R119" t="n">
-        <v>6791705</v>
+        <v>6791742</v>
       </c>
       <c r="S119" t="n">
         <v>9</v>
@@ -13559,7 +13549,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13569,7 +13559,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13589,39 +13579,39 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127697101</v>
+        <v>127697747</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13631,10 +13621,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>481033</v>
+        <v>481048</v>
       </c>
       <c r="R120" t="n">
-        <v>6791742</v>
+        <v>6791700</v>
       </c>
       <c r="S120" t="n">
         <v>9</v>
@@ -13666,7 +13656,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13676,7 +13666,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Betade tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13696,17 +13691,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127697747</v>
+        <v>127699098</v>
       </c>
       <c r="B121" t="n">
-        <v>56864</v>
+        <v>5177</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13714,37 +13709,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>481048</v>
+        <v>481041</v>
       </c>
       <c r="R121" t="n">
-        <v>6791700</v>
+        <v>6791490</v>
       </c>
       <c r="S121" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13783,12 +13783,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Betade tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13815,38 +13810,38 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127699098</v>
+        <v>127699090</v>
       </c>
       <c r="B122" t="n">
-        <v>5177</v>
+        <v>57672</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13855,13 +13850,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>481041</v>
+        <v>480970</v>
       </c>
       <c r="R122" t="n">
-        <v>6791490</v>
+        <v>6791562</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13927,10 +13922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127700636</v>
+        <v>127699075</v>
       </c>
       <c r="B123" t="n">
-        <v>79061</v>
+        <v>57832</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13938,37 +13933,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>481117</v>
+        <v>480958</v>
       </c>
       <c r="R123" t="n">
-        <v>6791518</v>
+        <v>6791568</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14034,7 +14034,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127697268</v>
+        <v>127702746</v>
       </c>
       <c r="B124" t="n">
         <v>79061</v>
@@ -14063,16 +14063,19 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>480976</v>
+        <v>481027</v>
       </c>
       <c r="R124" t="n">
-        <v>6791656</v>
+        <v>6791478</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14102,21 +14105,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>09:58</t>
-        </is>
-      </c>
       <c r="AC124" t="inlineStr">
         <is>
           <t>På gran</t>
@@ -14128,6 +14121,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14146,7 +14140,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127697104</v>
+        <v>127702694</v>
       </c>
       <c r="B125" t="n">
         <v>79061</v>
@@ -14175,19 +14169,22 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>481033</v>
+        <v>480974</v>
       </c>
       <c r="R125" t="n">
-        <v>6791742</v>
+        <v>6791516</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14214,19 +14211,14 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>09:44</t>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14235,28 +14227,29 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127698802</v>
+        <v>127697268</v>
       </c>
       <c r="B126" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14264,37 +14257,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>481014</v>
+        <v>480976</v>
       </c>
       <c r="R126" t="n">
-        <v>6791631</v>
+        <v>6791656</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14323,7 +14316,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14333,7 +14326,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14348,22 +14346,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127697283</v>
+        <v>127697104</v>
       </c>
       <c r="B127" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14371,34 +14369,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>481009</v>
+        <v>481033</v>
       </c>
       <c r="R127" t="n">
-        <v>6791717</v>
+        <v>6791742</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14430,7 +14428,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14440,7 +14438,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14455,65 +14453,65 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127698996</v>
+        <v>127699527</v>
       </c>
       <c r="B128" t="n">
-        <v>56864</v>
+        <v>57669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>480951</v>
+        <v>481147</v>
       </c>
       <c r="R128" t="n">
-        <v>6791482</v>
+        <v>6791614</v>
       </c>
       <c r="S128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14542,7 +14540,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14552,7 +14550,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14567,65 +14565,65 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127699527</v>
+        <v>127698996</v>
       </c>
       <c r="B129" t="n">
-        <v>57669</v>
+        <v>56864</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>481147</v>
+        <v>480951</v>
       </c>
       <c r="R129" t="n">
-        <v>6791614</v>
+        <v>6791482</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14654,7 +14652,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14664,7 +14662,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14679,22 +14677,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127702746</v>
+        <v>127698802</v>
       </c>
       <c r="B130" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14702,40 +14700,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>481027</v>
+        <v>481014</v>
       </c>
       <c r="R130" t="n">
-        <v>6791478</v>
+        <v>6791631</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14762,14 +14757,19 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14778,29 +14778,28 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127702694</v>
+        <v>127697283</v>
       </c>
       <c r="B131" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14808,40 +14807,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>480974</v>
+        <v>481009</v>
       </c>
       <c r="R131" t="n">
-        <v>6791516</v>
+        <v>6791717</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14868,14 +14864,19 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14884,29 +14885,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127698631</v>
+        <v>127699578</v>
       </c>
       <c r="B132" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14914,21 +14914,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>480930</v>
+        <v>481202</v>
       </c>
       <c r="R132" t="n">
-        <v>6791596</v>
+        <v>6791440</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15010,10 +15010,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127697242</v>
+        <v>127698631</v>
       </c>
       <c r="B133" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15021,21 +15021,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15045,10 +15045,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>481040</v>
+        <v>480930</v>
       </c>
       <c r="R133" t="n">
-        <v>6791735</v>
+        <v>6791596</v>
       </c>
       <c r="S133" t="n">
         <v>9</v>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15110,14 +15110,14 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127699578</v>
+        <v>127697242</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -15152,13 +15152,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>481202</v>
+        <v>481040</v>
       </c>
       <c r="R134" t="n">
-        <v>6791440</v>
+        <v>6791735</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15217,55 +15217,55 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127700845</v>
+        <v>127698999</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>481102</v>
+        <v>480951</v>
       </c>
       <c r="R135" t="n">
-        <v>6791567</v>
+        <v>6791482</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15319,57 +15319,62 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127698141</v>
+        <v>127699221</v>
       </c>
       <c r="B136" t="n">
-        <v>79061</v>
+        <v>5177</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>480972</v>
+        <v>481106</v>
       </c>
       <c r="R136" t="n">
-        <v>6791653</v>
+        <v>6791477</v>
       </c>
       <c r="S136" t="n">
         <v>9</v>
@@ -15401,7 +15406,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15411,7 +15416,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15438,10 +15443,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127697430</v>
+        <v>127698619</v>
       </c>
       <c r="B137" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15449,37 +15454,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>481051</v>
+        <v>480930</v>
       </c>
       <c r="R137" t="n">
-        <v>6791712</v>
+        <v>6791596</v>
       </c>
       <c r="S137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15508,7 +15518,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15518,7 +15528,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15545,48 +15555,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127698999</v>
+        <v>127700845</v>
       </c>
       <c r="B138" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480951</v>
+        <v>481102</v>
       </c>
       <c r="R138" t="n">
-        <v>6791482</v>
+        <v>6791567</v>
       </c>
       <c r="S138" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15615,7 +15625,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15625,7 +15635,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15640,62 +15650,57 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127699221</v>
+        <v>127698141</v>
       </c>
       <c r="B139" t="n">
-        <v>5177</v>
+        <v>79061</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>481106</v>
+        <v>480972</v>
       </c>
       <c r="R139" t="n">
-        <v>6791477</v>
+        <v>6791653</v>
       </c>
       <c r="S139" t="n">
         <v>9</v>
@@ -15727,7 +15732,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15737,7 +15742,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15764,10 +15769,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127698619</v>
+        <v>127697430</v>
       </c>
       <c r="B140" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15775,42 +15780,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>480930</v>
+        <v>481051</v>
       </c>
       <c r="R140" t="n">
-        <v>6791596</v>
+        <v>6791712</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17623,38 +17623,38 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127698374</v>
+        <v>127699095</v>
       </c>
       <c r="B157" t="n">
-        <v>57672</v>
+        <v>5177</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -17663,13 +17663,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>480934</v>
+        <v>480970</v>
       </c>
       <c r="R157" t="n">
-        <v>6791623</v>
+        <v>6791562</v>
       </c>
       <c r="S157" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17735,10 +17735,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127699297</v>
+        <v>127698374</v>
       </c>
       <c r="B158" t="n">
-        <v>79618</v>
+        <v>57672</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17746,37 +17746,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>481074</v>
+        <v>480934</v>
       </c>
       <c r="R158" t="n">
-        <v>6791631</v>
+        <v>6791623</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17805,7 +17810,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17815,7 +17820,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17830,50 +17835,54 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127699095</v>
+        <v>127698885</v>
       </c>
       <c r="B159" t="n">
-        <v>5177</v>
+        <v>57832</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -17882,13 +17891,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>480970</v>
+        <v>480932</v>
       </c>
       <c r="R159" t="n">
-        <v>6791562</v>
+        <v>6791598</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17917,7 +17926,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17927,7 +17936,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17954,54 +17963,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127698885</v>
+        <v>127699451</v>
       </c>
       <c r="B160" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>480932</v>
+        <v>481157</v>
       </c>
       <c r="R160" t="n">
-        <v>6791598</v>
+        <v>6791437</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18033,7 +18033,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18043,7 +18043,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18070,45 +18070,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127699451</v>
+        <v>127699297</v>
       </c>
       <c r="B161" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>481157</v>
+        <v>481074</v>
       </c>
       <c r="R161" t="n">
-        <v>6791437</v>
+        <v>6791631</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18140,7 +18140,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18165,12 +18165,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127702760</v>
+        <v>127698286</v>
       </c>
       <c r="B2" t="n">
-        <v>79061</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedvasslan, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481025</v>
+        <v>480923</v>
       </c>
       <c r="R2" t="n">
-        <v>6791487</v>
+        <v>6791625</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,14 +748,19 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,29 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127700382</v>
+        <v>127697277</v>
       </c>
       <c r="B3" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481161</v>
+        <v>481009</v>
       </c>
       <c r="R3" t="n">
-        <v>6791478</v>
+        <v>6791717</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -861,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,60 +882,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127700590</v>
+        <v>127698283</v>
       </c>
       <c r="B4" t="n">
-        <v>92654</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481137</v>
+        <v>480987</v>
       </c>
       <c r="R4" t="n">
-        <v>6791517</v>
+        <v>6791630</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,19 +989,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127701512</v>
+        <v>127697408</v>
       </c>
       <c r="B5" t="n">
         <v>57672</v>
@@ -1031,7 +1032,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481100</v>
+        <v>481078</v>
       </c>
       <c r="R5" t="n">
-        <v>6791578</v>
+        <v>6791705</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1075,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127697277</v>
+        <v>127702760</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,37 +1124,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481009</v>
+        <v>481025</v>
       </c>
       <c r="R6" t="n">
-        <v>6791717</v>
+        <v>6791487</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,19 +1184,14 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:34</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,28 +1200,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127698283</v>
+        <v>127700382</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480987</v>
+        <v>481161</v>
       </c>
       <c r="R7" t="n">
-        <v>6791630</v>
+        <v>6791478</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1299,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,65 +1319,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127698286</v>
+        <v>127700590</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>92654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480923</v>
+        <v>481137</v>
       </c>
       <c r="R8" t="n">
-        <v>6791625</v>
+        <v>6791517</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127697408</v>
+        <v>127701512</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1469,7 +1469,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481078</v>
+        <v>481100</v>
       </c>
       <c r="R9" t="n">
-        <v>6791705</v>
+        <v>6791578</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127696907</v>
+        <v>127698633</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480962</v>
+        <v>480987</v>
       </c>
       <c r="R10" t="n">
-        <v>6791703</v>
+        <v>6791597</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,48 +1657,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127696901</v>
+        <v>127699393</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480963</v>
+        <v>481124</v>
       </c>
       <c r="R11" t="n">
-        <v>6791715</v>
+        <v>6791490</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,17 +1762,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700714</v>
+        <v>127697865</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,37 +1780,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481095</v>
+        <v>481006</v>
       </c>
       <c r="R12" t="n">
-        <v>6791538</v>
+        <v>6791677</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1834,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,19 +1864,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127698633</v>
+        <v>127700714</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1906,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480987</v>
+        <v>481095</v>
       </c>
       <c r="R13" t="n">
-        <v>6791597</v>
+        <v>6791538</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,50 +1983,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127699393</v>
+        <v>127696907</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481124</v>
+        <v>480962</v>
       </c>
       <c r="R14" t="n">
-        <v>6791490</v>
+        <v>6791703</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,22 +2078,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127697865</v>
+        <v>127696901</v>
       </c>
       <c r="B15" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481006</v>
+        <v>480963</v>
       </c>
       <c r="R15" t="n">
-        <v>6791677</v>
+        <v>6791715</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,17 +2190,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127701188</v>
+        <v>127698067</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,39 +2208,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481073</v>
+        <v>480997</v>
       </c>
       <c r="R16" t="n">
-        <v>6791616</v>
+        <v>6791673</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2272,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,7 +2277,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2309,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127698067</v>
+        <v>127697100</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2340,17 +2335,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480997</v>
+        <v>481032</v>
       </c>
       <c r="R17" t="n">
-        <v>6791673</v>
+        <v>6791729</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2384,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,19 +2399,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127697100</v>
+        <v>127697311</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2447,17 +2442,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481032</v>
+        <v>481070</v>
       </c>
       <c r="R18" t="n">
-        <v>6791729</v>
+        <v>6791717</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2496,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,19 +2506,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127697311</v>
+        <v>127698861</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2554,17 +2549,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481070</v>
+        <v>481024</v>
       </c>
       <c r="R19" t="n">
-        <v>6791717</v>
+        <v>6791620</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2593,7 +2588,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,7 +2598,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,22 +2613,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127698861</v>
+        <v>127699269</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,34 +2636,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481024</v>
+        <v>481074</v>
       </c>
       <c r="R20" t="n">
-        <v>6791620</v>
+        <v>6791631</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127699033</v>
+        <v>127698539</v>
       </c>
       <c r="B21" t="n">
         <v>5177</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480958</v>
+        <v>480934</v>
       </c>
       <c r="R21" t="n">
-        <v>6791568</v>
+        <v>6791623</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,53 +2849,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127699269</v>
+        <v>127699033</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481074</v>
+        <v>480958</v>
       </c>
       <c r="R22" t="n">
-        <v>6791631</v>
+        <v>6791568</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,12 +2949,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3068,38 +3068,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127698539</v>
+        <v>127701188</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480934</v>
+        <v>481073</v>
       </c>
       <c r="R24" t="n">
-        <v>6791623</v>
+        <v>6791616</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5802,10 +5802,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127701141</v>
+        <v>127696761</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5813,37 +5813,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481104</v>
+        <v>480912</v>
       </c>
       <c r="R49" t="n">
-        <v>6791603</v>
+        <v>6791695</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5897,19 +5897,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127700359</v>
+        <v>127697066</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5940,17 +5940,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481190</v>
+        <v>480998</v>
       </c>
       <c r="R50" t="n">
-        <v>6791470</v>
+        <v>6791729</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6004,57 +6004,62 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127696761</v>
+        <v>127698857</v>
       </c>
       <c r="B51" t="n">
-        <v>79061</v>
+        <v>5177</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480912</v>
+        <v>480934</v>
       </c>
       <c r="R51" t="n">
-        <v>6791695</v>
+        <v>6791542</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
@@ -6086,7 +6091,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6096,7 +6101,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6116,17 +6121,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127697066</v>
+        <v>127697743</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6134,34 +6139,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480998</v>
+        <v>481048</v>
       </c>
       <c r="R52" t="n">
-        <v>6791729</v>
+        <v>6791700</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6193,7 +6203,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6203,7 +6213,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6223,17 +6233,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127698857</v>
+        <v>127699193</v>
       </c>
       <c r="B53" t="n">
-        <v>5177</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6241,21 +6251,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6270,13 +6280,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480934</v>
+        <v>480980</v>
       </c>
       <c r="R53" t="n">
-        <v>6791542</v>
+        <v>6791570</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6305,7 +6315,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6315,7 +6325,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6342,10 +6352,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127697743</v>
+        <v>127701141</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6353,42 +6363,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481048</v>
+        <v>481104</v>
       </c>
       <c r="R54" t="n">
-        <v>6791700</v>
+        <v>6791603</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6417,7 +6422,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6427,7 +6432,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6442,62 +6447,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127699193</v>
+        <v>127700359</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480980</v>
+        <v>481190</v>
       </c>
       <c r="R55" t="n">
-        <v>6791570</v>
+        <v>6791470</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6554,12 +6554,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6897,38 +6897,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127699410</v>
+        <v>127696742</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6937,10 +6946,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481141</v>
+        <v>480917</v>
       </c>
       <c r="R59" t="n">
-        <v>6791461</v>
+        <v>6791694</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6972,7 +6981,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6982,7 +6991,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7009,48 +7018,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127700960</v>
+        <v>127698994</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481132</v>
+        <v>480949</v>
       </c>
       <c r="R60" t="n">
-        <v>6791620</v>
+        <v>6791564</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7079,7 +7093,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7089,7 +7103,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7104,59 +7118,50 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127696742</v>
+        <v>127699410</v>
       </c>
       <c r="B61" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7165,10 +7170,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480917</v>
+        <v>481141</v>
       </c>
       <c r="R61" t="n">
-        <v>6791694</v>
+        <v>6791461</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7200,7 +7205,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7210,7 +7215,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7237,10 +7242,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127698994</v>
+        <v>127697046</v>
       </c>
       <c r="B62" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7248,27 +7253,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7277,10 +7282,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480949</v>
+        <v>480998</v>
       </c>
       <c r="R62" t="n">
-        <v>6791564</v>
+        <v>6791729</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7312,7 +7317,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7322,7 +7327,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7342,17 +7347,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127697046</v>
+        <v>127699111</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7360,21 +7365,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7389,13 +7394,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480998</v>
+        <v>481041</v>
       </c>
       <c r="R63" t="n">
-        <v>6791729</v>
+        <v>6791490</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7424,7 +7429,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7434,7 +7439,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7454,17 +7459,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127699111</v>
+        <v>127698670</v>
       </c>
       <c r="B64" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7472,21 +7477,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7501,13 +7506,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481041</v>
+        <v>480930</v>
       </c>
       <c r="R64" t="n">
-        <v>6791490</v>
+        <v>6791596</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7536,7 +7541,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7546,7 +7551,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7573,53 +7578,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127698670</v>
+        <v>127700960</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480930</v>
+        <v>481132</v>
       </c>
       <c r="R65" t="n">
-        <v>6791596</v>
+        <v>6791620</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7673,12 +7673,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127699161</v>
+        <v>127699017</v>
       </c>
       <c r="B82" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9463,21 +9463,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>480980</v>
+        <v>481001</v>
       </c>
       <c r="R82" t="n">
-        <v>6791570</v>
+        <v>6791490</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9559,10 +9559,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127699309</v>
+        <v>127700777</v>
       </c>
       <c r="B83" t="n">
-        <v>78788</v>
+        <v>79618</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9570,21 +9570,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481074</v>
+        <v>481102</v>
       </c>
       <c r="R83" t="n">
-        <v>6791631</v>
+        <v>6791567</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9666,32 +9666,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127700910</v>
+        <v>127699161</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>79618</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9701,13 +9701,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481139</v>
+        <v>480980</v>
       </c>
       <c r="R84" t="n">
-        <v>6791575</v>
+        <v>6791570</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9773,54 +9773,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127700837</v>
+        <v>127699309</v>
       </c>
       <c r="B85" t="n">
-        <v>56864</v>
+        <v>78788</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481147</v>
+        <v>481074</v>
       </c>
       <c r="R85" t="n">
-        <v>6791569</v>
+        <v>6791631</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9852,7 +9843,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9862,7 +9853,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9877,22 +9868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127700777</v>
+        <v>127700371</v>
       </c>
       <c r="B86" t="n">
-        <v>79618</v>
+        <v>91352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9900,34 +9891,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481102</v>
+        <v>481171</v>
       </c>
       <c r="R86" t="n">
-        <v>6791567</v>
+        <v>6791459</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9959,7 +9950,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9969,7 +9960,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9984,19 +9975,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127699017</v>
+        <v>127700455</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -10027,14 +10018,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481001</v>
+        <v>481162</v>
       </c>
       <c r="R87" t="n">
-        <v>6791490</v>
+        <v>6791491</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10066,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10076,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10091,12 +10082,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10210,32 +10201,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127700371</v>
+        <v>127700910</v>
       </c>
       <c r="B89" t="n">
-        <v>91352</v>
+        <v>92642</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10245,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481171</v>
+        <v>481139</v>
       </c>
       <c r="R89" t="n">
-        <v>6791459</v>
+        <v>6791575</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10317,10 +10308,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127700455</v>
+        <v>127700497</v>
       </c>
       <c r="B90" t="n">
-        <v>79029</v>
+        <v>75153</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10328,21 +10319,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10352,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481162</v>
+        <v>481155</v>
       </c>
       <c r="R90" t="n">
-        <v>6791491</v>
+        <v>6791512</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10424,10 +10415,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127700497</v>
+        <v>127700823</v>
       </c>
       <c r="B91" t="n">
-        <v>75153</v>
+        <v>57669</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10435,37 +10426,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481155</v>
+        <v>481147</v>
       </c>
       <c r="R91" t="n">
-        <v>6791512</v>
+        <v>6791569</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10494,7 +10490,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10504,7 +10500,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10519,50 +10515,54 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127700823</v>
+        <v>127700837</v>
       </c>
       <c r="B92" t="n">
-        <v>57669</v>
+        <v>56864</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10577,7 +10577,7 @@
         <v>6791569</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10643,45 +10643,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127698937</v>
+        <v>127699374</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>480949</v>
+        <v>481074</v>
       </c>
       <c r="R93" t="n">
-        <v>6791564</v>
+        <v>6791631</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10738,22 +10738,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127699026</v>
+        <v>127698937</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10761,34 +10761,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>481040</v>
+        <v>480949</v>
       </c>
       <c r="R94" t="n">
-        <v>6791597</v>
+        <v>6791564</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10845,22 +10845,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127696785</v>
+        <v>127697267</v>
       </c>
       <c r="B95" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10868,37 +10868,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480937</v>
+        <v>481070</v>
       </c>
       <c r="R95" t="n">
-        <v>6791705</v>
+        <v>6791717</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10927,7 +10932,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10937,7 +10942,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10952,60 +10957,65 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127697854</v>
+        <v>127697901</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481035</v>
+        <v>481006</v>
       </c>
       <c r="R96" t="n">
-        <v>6791695</v>
+        <v>6791673</v>
       </c>
       <c r="S96" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11034,7 +11044,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11044,7 +11054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11059,22 +11069,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127697267</v>
+        <v>127699307</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11082,42 +11092,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481070</v>
+        <v>481074</v>
       </c>
       <c r="R97" t="n">
-        <v>6791717</v>
+        <v>6791631</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11146,7 +11151,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11156,7 +11161,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11171,50 +11176,50 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127697901</v>
+        <v>127699200</v>
       </c>
       <c r="B98" t="n">
-        <v>56864</v>
+        <v>57669</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11223,10 +11228,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>481006</v>
+        <v>480980</v>
       </c>
       <c r="R98" t="n">
-        <v>6791673</v>
+        <v>6791570</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -11258,7 +11263,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11268,7 +11273,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11295,32 +11300,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127699374</v>
+        <v>127699026</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11330,10 +11335,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481074</v>
+        <v>481040</v>
       </c>
       <c r="R99" t="n">
-        <v>6791631</v>
+        <v>6791597</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11402,10 +11407,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127699307</v>
+        <v>127696785</v>
       </c>
       <c r="B100" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11413,21 +11418,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11437,10 +11442,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>481074</v>
+        <v>480937</v>
       </c>
       <c r="R100" t="n">
-        <v>6791631</v>
+        <v>6791705</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11509,10 +11514,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127699200</v>
+        <v>127697854</v>
       </c>
       <c r="B101" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11520,42 +11525,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>480980</v>
+        <v>481035</v>
       </c>
       <c r="R101" t="n">
-        <v>6791570</v>
+        <v>6791695</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11609,12 +11609,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11961,32 +11961,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127699081</v>
+        <v>127697059</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11996,13 +11996,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480958</v>
+        <v>480998</v>
       </c>
       <c r="R105" t="n">
-        <v>6791568</v>
+        <v>6791729</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12061,39 +12061,39 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127697411</v>
+        <v>127699081</v>
       </c>
       <c r="B106" t="n">
-        <v>79618</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12103,13 +12103,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>481081</v>
+        <v>480958</v>
       </c>
       <c r="R106" t="n">
-        <v>6791711</v>
+        <v>6791568</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12148,12 +12148,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På roten av en gammal tallåga</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12168,44 +12163,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127701548</v>
+        <v>127697411</v>
       </c>
       <c r="B107" t="n">
-        <v>91317</v>
+        <v>79618</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12215,13 +12210,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>481100</v>
+        <v>481081</v>
       </c>
       <c r="R107" t="n">
-        <v>6791578</v>
+        <v>6791711</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12250,7 +12245,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12260,7 +12255,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>På roten av en gammal tallåga</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12275,44 +12275,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127697059</v>
+        <v>127701548</v>
       </c>
       <c r="B108" t="n">
-        <v>79061</v>
+        <v>91317</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12322,13 +12322,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>480998</v>
+        <v>481100</v>
       </c>
       <c r="R108" t="n">
-        <v>6791729</v>
+        <v>6791578</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12387,57 +12387,52 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127701318</v>
+        <v>127696731</v>
       </c>
       <c r="B109" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>481100</v>
+        <v>480916</v>
       </c>
       <c r="R109" t="n">
-        <v>6791578</v>
+        <v>6791696</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12469,7 +12464,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12479,7 +12474,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12494,22 +12489,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127698632</v>
+        <v>127698216</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12517,42 +12512,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480963</v>
+        <v>480972</v>
       </c>
       <c r="R110" t="n">
-        <v>6791579</v>
+        <v>6791653</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12581,7 +12571,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12591,7 +12581,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12606,39 +12596,39 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127698322</v>
+        <v>127698632</v>
       </c>
       <c r="B111" t="n">
-        <v>5197</v>
+        <v>57672</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12647,19 +12637,24 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480936</v>
+        <v>480963</v>
       </c>
       <c r="R111" t="n">
-        <v>6791610</v>
+        <v>6791579</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12688,7 +12683,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12698,7 +12693,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12713,12 +12708,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12837,48 +12832,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127696731</v>
+        <v>127698322</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480916</v>
+        <v>480936</v>
       </c>
       <c r="R113" t="n">
-        <v>6791696</v>
+        <v>6791610</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12907,7 +12902,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12917,7 +12912,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12932,60 +12927,65 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127698216</v>
+        <v>127701318</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>480972</v>
+        <v>481100</v>
       </c>
       <c r="R114" t="n">
-        <v>6791653</v>
+        <v>6791578</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13051,10 +13051,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127700636</v>
+        <v>127697443</v>
       </c>
       <c r="B115" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13062,37 +13062,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>481117</v>
+        <v>481071</v>
       </c>
       <c r="R115" t="n">
-        <v>6791518</v>
+        <v>6791709</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13146,19 +13146,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127697443</v>
+        <v>127699444</v>
       </c>
       <c r="B116" t="n">
         <v>79029</v>
@@ -13189,14 +13189,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>481071</v>
+        <v>481127</v>
       </c>
       <c r="R116" t="n">
-        <v>6791709</v>
+        <v>6791446</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13253,22 +13253,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127699444</v>
+        <v>127699090</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13276,34 +13276,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>481127</v>
+        <v>480970</v>
       </c>
       <c r="R117" t="n">
-        <v>6791446</v>
+        <v>6791562</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13335,7 +13340,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13345,7 +13350,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13372,48 +13377,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127697402</v>
+        <v>127699075</v>
       </c>
       <c r="B118" t="n">
-        <v>92646</v>
+        <v>57832</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>481078</v>
+        <v>480958</v>
       </c>
       <c r="R118" t="n">
-        <v>6791705</v>
+        <v>6791568</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13442,7 +13452,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13452,7 +13462,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13479,32 +13489,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127697101</v>
+        <v>127697402</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>92646</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13514,10 +13524,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>481033</v>
+        <v>481078</v>
       </c>
       <c r="R119" t="n">
-        <v>6791742</v>
+        <v>6791705</v>
       </c>
       <c r="S119" t="n">
         <v>9</v>
@@ -13549,7 +13559,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13559,7 +13569,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13579,39 +13589,39 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127697747</v>
+        <v>127697101</v>
       </c>
       <c r="B120" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13621,10 +13631,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>481048</v>
+        <v>481033</v>
       </c>
       <c r="R120" t="n">
-        <v>6791700</v>
+        <v>6791742</v>
       </c>
       <c r="S120" t="n">
         <v>9</v>
@@ -13656,7 +13666,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13666,12 +13676,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Betade tall</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13691,17 +13696,17 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127699098</v>
+        <v>127697747</v>
       </c>
       <c r="B121" t="n">
-        <v>5177</v>
+        <v>56864</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13709,42 +13714,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>481041</v>
+        <v>481048</v>
       </c>
       <c r="R121" t="n">
-        <v>6791490</v>
+        <v>6791700</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13783,7 +13783,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Betade tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13810,38 +13815,38 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127699090</v>
+        <v>127699098</v>
       </c>
       <c r="B122" t="n">
-        <v>57672</v>
+        <v>5177</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13850,13 +13855,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>480970</v>
+        <v>481041</v>
       </c>
       <c r="R122" t="n">
-        <v>6791562</v>
+        <v>6791490</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13922,10 +13927,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127699075</v>
+        <v>127700636</v>
       </c>
       <c r="B123" t="n">
-        <v>57832</v>
+        <v>79061</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13933,42 +13938,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>480958</v>
+        <v>481117</v>
       </c>
       <c r="R123" t="n">
-        <v>6791568</v>
+        <v>6791518</v>
       </c>
       <c r="S123" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16421,10 +16421,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127701082</v>
+        <v>127698695</v>
       </c>
       <c r="B146" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16432,37 +16432,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>481130</v>
+        <v>481002</v>
       </c>
       <c r="R146" t="n">
-        <v>6791622</v>
+        <v>6791612</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16501,12 +16501,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16521,19 +16516,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127698695</v>
+        <v>127698677</v>
       </c>
       <c r="B147" t="n">
         <v>79029</v>
@@ -16568,10 +16563,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>481002</v>
+        <v>480990</v>
       </c>
       <c r="R147" t="n">
-        <v>6791612</v>
+        <v>6791599</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16640,7 +16635,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127698677</v>
+        <v>127698427</v>
       </c>
       <c r="B148" t="n">
         <v>79029</v>
@@ -16675,10 +16670,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>480990</v>
+        <v>480971</v>
       </c>
       <c r="R148" t="n">
-        <v>6791599</v>
+        <v>6791584</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16721,6 +16716,11 @@
       <c r="AB148" t="inlineStr">
         <is>
           <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16747,7 +16747,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127698427</v>
+        <v>127699478</v>
       </c>
       <c r="B149" t="n">
         <v>79029</v>
@@ -16782,10 +16782,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>480971</v>
+        <v>481142</v>
       </c>
       <c r="R149" t="n">
-        <v>6791584</v>
+        <v>6791632</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16828,11 +16828,6 @@
       <c r="AB149" t="inlineStr">
         <is>
           <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16859,7 +16854,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127699478</v>
+        <v>127700440</v>
       </c>
       <c r="B150" t="n">
         <v>79029</v>
@@ -16894,10 +16889,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>481142</v>
+        <v>481160</v>
       </c>
       <c r="R150" t="n">
-        <v>6791632</v>
+        <v>6791480</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16929,7 +16924,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16939,7 +16934,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16966,53 +16961,48 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127698347</v>
+        <v>127701082</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>79061</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>480936</v>
+        <v>481130</v>
       </c>
       <c r="R151" t="n">
-        <v>6791610</v>
+        <v>6791622</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17041,7 +17031,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17051,7 +17041,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17066,12 +17061,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -17297,45 +17292,50 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127700440</v>
+        <v>127698347</v>
       </c>
       <c r="B154" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>481160</v>
+        <v>480936</v>
       </c>
       <c r="R154" t="n">
-        <v>6791480</v>
+        <v>6791610</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17367,7 +17367,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17392,12 +17392,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127698067</v>
+        <v>127701188</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480997</v>
+        <v>481073</v>
       </c>
       <c r="R16" t="n">
-        <v>6791673</v>
+        <v>6791616</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2267,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2282,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2309,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127697100</v>
+        <v>127698067</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2335,17 +2340,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481032</v>
+        <v>480997</v>
       </c>
       <c r="R17" t="n">
-        <v>6791729</v>
+        <v>6791673</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2374,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,19 +2404,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127697311</v>
+        <v>127697100</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2442,17 +2447,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481070</v>
+        <v>481032</v>
       </c>
       <c r="R18" t="n">
-        <v>6791717</v>
+        <v>6791729</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2496,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,19 +2511,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127698861</v>
+        <v>127697311</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2549,17 +2554,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481024</v>
+        <v>481070</v>
       </c>
       <c r="R19" t="n">
-        <v>6791620</v>
+        <v>6791717</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2603,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,22 +2618,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127699269</v>
+        <v>127698861</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,39 +2641,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481074</v>
+        <v>481024</v>
       </c>
       <c r="R20" t="n">
-        <v>6791631</v>
+        <v>6791620</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127698539</v>
+        <v>127699033</v>
       </c>
       <c r="B21" t="n">
         <v>5177</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480934</v>
+        <v>480958</v>
       </c>
       <c r="R21" t="n">
-        <v>6791623</v>
+        <v>6791568</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,53 +2849,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127699033</v>
+        <v>127699269</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480958</v>
+        <v>481074</v>
       </c>
       <c r="R22" t="n">
-        <v>6791568</v>
+        <v>6791631</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,12 +2949,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3068,38 +3068,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127701188</v>
+        <v>127698539</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>5177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481073</v>
+        <v>480934</v>
       </c>
       <c r="R24" t="n">
-        <v>6791616</v>
+        <v>6791623</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3832,32 +3832,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127697912</v>
+        <v>127698467</v>
       </c>
       <c r="B31" t="n">
-        <v>79061</v>
+        <v>91513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481035</v>
+        <v>480934</v>
       </c>
       <c r="R31" t="n">
-        <v>6791685</v>
+        <v>6791623</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3912,12 +3912,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,44 +3927,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127698467</v>
+        <v>127697912</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>79061</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3979,13 +3974,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480934</v>
+        <v>481035</v>
       </c>
       <c r="R32" t="n">
-        <v>6791623</v>
+        <v>6791685</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4014,7 +4009,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4024,7 +4019,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,19 +4039,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127697212</v>
+        <v>127699069</v>
       </c>
       <c r="B33" t="n">
         <v>79029</v>
@@ -4086,13 +4086,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481033</v>
+        <v>480958</v>
       </c>
       <c r="R33" t="n">
-        <v>6791734</v>
+        <v>6791568</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4151,14 +4151,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127699069</v>
+        <v>127697081</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -4189,17 +4189,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480958</v>
+        <v>481024</v>
       </c>
       <c r="R34" t="n">
-        <v>6791568</v>
+        <v>6791701</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,19 +4253,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127697081</v>
+        <v>127697212</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4296,17 +4296,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481024</v>
+        <v>481033</v>
       </c>
       <c r="R35" t="n">
-        <v>6791701</v>
+        <v>6791734</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -6897,47 +6897,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127696742</v>
+        <v>127699410</v>
       </c>
       <c r="B59" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6946,10 +6937,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480917</v>
+        <v>481141</v>
       </c>
       <c r="R59" t="n">
-        <v>6791694</v>
+        <v>6791461</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6981,7 +6972,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6991,7 +6982,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7018,53 +7009,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127698994</v>
+        <v>127700960</v>
       </c>
       <c r="B60" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480949</v>
+        <v>481132</v>
       </c>
       <c r="R60" t="n">
-        <v>6791564</v>
+        <v>6791620</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7093,7 +7079,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7103,7 +7089,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7118,50 +7104,59 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127699410</v>
+        <v>127696742</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7170,10 +7165,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481141</v>
+        <v>480917</v>
       </c>
       <c r="R61" t="n">
-        <v>6791461</v>
+        <v>6791694</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7205,7 +7200,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7215,7 +7210,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7242,10 +7237,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127697046</v>
+        <v>127698994</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7253,27 +7248,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7282,10 +7277,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480998</v>
+        <v>480949</v>
       </c>
       <c r="R62" t="n">
-        <v>6791729</v>
+        <v>6791564</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7317,7 +7312,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7327,7 +7322,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7347,17 +7342,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127699111</v>
+        <v>127697046</v>
       </c>
       <c r="B63" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7365,21 +7360,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7394,13 +7389,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481041</v>
+        <v>480998</v>
       </c>
       <c r="R63" t="n">
-        <v>6791490</v>
+        <v>6791729</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7429,7 +7424,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7439,7 +7434,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7459,17 +7454,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127698670</v>
+        <v>127699111</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7477,21 +7472,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7506,13 +7501,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480930</v>
+        <v>481041</v>
       </c>
       <c r="R64" t="n">
-        <v>6791596</v>
+        <v>6791490</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7541,7 +7536,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7551,7 +7546,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7578,48 +7573,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127700960</v>
+        <v>127698670</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481132</v>
+        <v>480930</v>
       </c>
       <c r="R65" t="n">
-        <v>6791620</v>
+        <v>6791596</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7673,12 +7673,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127699017</v>
+        <v>127700777</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9463,34 +9463,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481001</v>
+        <v>481102</v>
       </c>
       <c r="R82" t="n">
-        <v>6791490</v>
+        <v>6791567</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9547,19 +9547,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127700777</v>
+        <v>127699161</v>
       </c>
       <c r="B83" t="n">
         <v>79618</v>
@@ -9590,17 +9590,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481102</v>
+        <v>480980</v>
       </c>
       <c r="R83" t="n">
-        <v>6791567</v>
+        <v>6791570</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9654,22 +9654,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127699161</v>
+        <v>127699309</v>
       </c>
       <c r="B84" t="n">
-        <v>79618</v>
+        <v>78788</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9677,37 +9677,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>480980</v>
+        <v>481074</v>
       </c>
       <c r="R84" t="n">
-        <v>6791570</v>
+        <v>6791631</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9761,22 +9761,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127699309</v>
+        <v>127700371</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>91352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9784,34 +9784,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481074</v>
+        <v>481171</v>
       </c>
       <c r="R85" t="n">
-        <v>6791631</v>
+        <v>6791459</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9868,22 +9868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127700371</v>
+        <v>127700455</v>
       </c>
       <c r="B86" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9891,34 +9891,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481171</v>
+        <v>481162</v>
       </c>
       <c r="R86" t="n">
-        <v>6791459</v>
+        <v>6791491</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9975,19 +9975,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127700455</v>
+        <v>127696956</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -10018,17 +10018,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481162</v>
+        <v>480973</v>
       </c>
       <c r="R87" t="n">
-        <v>6791491</v>
+        <v>6791733</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10082,19 +10082,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127696956</v>
+        <v>127699017</v>
       </c>
       <c r="B88" t="n">
         <v>79029</v>
@@ -10129,13 +10129,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>480973</v>
+        <v>481001</v>
       </c>
       <c r="R88" t="n">
-        <v>6791733</v>
+        <v>6791490</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10643,45 +10643,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127699374</v>
+        <v>127698937</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>481074</v>
+        <v>480949</v>
       </c>
       <c r="R93" t="n">
-        <v>6791631</v>
+        <v>6791564</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10738,22 +10738,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127698937</v>
+        <v>127699026</v>
       </c>
       <c r="B94" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10761,34 +10761,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>480949</v>
+        <v>481040</v>
       </c>
       <c r="R94" t="n">
-        <v>6791564</v>
+        <v>6791597</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10845,22 +10845,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127697267</v>
+        <v>127696785</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10868,42 +10868,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>481070</v>
+        <v>480937</v>
       </c>
       <c r="R95" t="n">
-        <v>6791717</v>
+        <v>6791705</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10932,7 +10927,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10942,7 +10937,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10957,65 +10952,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127697901</v>
+        <v>127697854</v>
       </c>
       <c r="B96" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>481006</v>
+        <v>481035</v>
       </c>
       <c r="R96" t="n">
-        <v>6791673</v>
+        <v>6791695</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11044,7 +11034,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11054,7 +11044,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11069,22 +11059,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127699307</v>
+        <v>127697267</v>
       </c>
       <c r="B97" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11092,37 +11082,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>481074</v>
+        <v>481070</v>
       </c>
       <c r="R97" t="n">
-        <v>6791631</v>
+        <v>6791717</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11151,7 +11146,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11161,7 +11156,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11176,50 +11171,50 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127699200</v>
+        <v>127697901</v>
       </c>
       <c r="B98" t="n">
-        <v>57669</v>
+        <v>56864</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11228,10 +11223,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>480980</v>
+        <v>481006</v>
       </c>
       <c r="R98" t="n">
-        <v>6791570</v>
+        <v>6791673</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -11263,7 +11258,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11273,7 +11268,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11300,32 +11295,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127699026</v>
+        <v>127699374</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11335,10 +11330,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>481040</v>
+        <v>481074</v>
       </c>
       <c r="R99" t="n">
-        <v>6791597</v>
+        <v>6791631</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11407,10 +11402,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127696785</v>
+        <v>127699307</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11418,21 +11413,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11442,10 +11437,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>480937</v>
+        <v>481074</v>
       </c>
       <c r="R100" t="n">
-        <v>6791705</v>
+        <v>6791631</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11514,10 +11509,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127697854</v>
+        <v>127699200</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11525,37 +11520,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>481035</v>
+        <v>480980</v>
       </c>
       <c r="R101" t="n">
-        <v>6791695</v>
+        <v>6791570</v>
       </c>
       <c r="S101" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11609,12 +11609,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -15224,48 +15224,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127698999</v>
+        <v>127700845</v>
       </c>
       <c r="B135" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>480951</v>
+        <v>481102</v>
       </c>
       <c r="R135" t="n">
-        <v>6791482</v>
+        <v>6791567</v>
       </c>
       <c r="S135" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15319,62 +15319,57 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127699221</v>
+        <v>127698141</v>
       </c>
       <c r="B136" t="n">
-        <v>5177</v>
+        <v>79061</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>481106</v>
+        <v>480972</v>
       </c>
       <c r="R136" t="n">
-        <v>6791477</v>
+        <v>6791653</v>
       </c>
       <c r="S136" t="n">
         <v>9</v>
@@ -15406,7 +15401,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15416,7 +15411,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15443,10 +15438,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127698619</v>
+        <v>127697430</v>
       </c>
       <c r="B137" t="n">
-        <v>57672</v>
+        <v>79061</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15454,42 +15449,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>480930</v>
+        <v>481051</v>
       </c>
       <c r="R137" t="n">
-        <v>6791596</v>
+        <v>6791712</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15518,7 +15508,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15528,7 +15518,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15555,48 +15545,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127700845</v>
+        <v>127698999</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>481102</v>
+        <v>480951</v>
       </c>
       <c r="R138" t="n">
-        <v>6791567</v>
+        <v>6791482</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15625,7 +15615,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15635,7 +15625,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15650,57 +15640,62 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127698141</v>
+        <v>127699221</v>
       </c>
       <c r="B139" t="n">
-        <v>79061</v>
+        <v>5177</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480972</v>
+        <v>481106</v>
       </c>
       <c r="R139" t="n">
-        <v>6791653</v>
+        <v>6791477</v>
       </c>
       <c r="S139" t="n">
         <v>9</v>
@@ -15732,7 +15727,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15742,7 +15737,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15769,10 +15764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127697430</v>
+        <v>127698619</v>
       </c>
       <c r="B140" t="n">
-        <v>79061</v>
+        <v>57672</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15780,37 +15775,42 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>481051</v>
+        <v>480930</v>
       </c>
       <c r="R140" t="n">
-        <v>6791712</v>
+        <v>6791596</v>
       </c>
       <c r="S140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD140" t="b">

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127697311</v>
+        <v>127698861</v>
       </c>
       <c r="B16" t="n">
         <v>79032</v>
@@ -2228,17 +2228,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481070</v>
+        <v>481024</v>
       </c>
       <c r="R16" t="n">
-        <v>6791717</v>
+        <v>6791620</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2292,22 +2292,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127699269</v>
+        <v>127697100</v>
       </c>
       <c r="B17" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,39 +2315,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481074</v>
+        <v>481032</v>
       </c>
       <c r="R17" t="n">
-        <v>6791631</v>
+        <v>6791729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,50 +2411,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127699033</v>
+        <v>127698067</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480958</v>
+        <v>480997</v>
       </c>
       <c r="R18" t="n">
-        <v>6791568</v>
+        <v>6791673</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2491,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,45 +2518,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127698355</v>
+        <v>127699269</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480971</v>
+        <v>481074</v>
       </c>
       <c r="R19" t="n">
-        <v>6791584</v>
+        <v>6791631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,48 +2630,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127698861</v>
+        <v>127698539</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481024</v>
+        <v>480934</v>
       </c>
       <c r="R20" t="n">
-        <v>6791620</v>
+        <v>6791623</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,60 +2730,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127697100</v>
+        <v>127699033</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481032</v>
+        <v>480958</v>
       </c>
       <c r="R21" t="n">
-        <v>6791729</v>
+        <v>6791568</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2812,7 +2817,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2822,7 +2827,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,19 +2842,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127698067</v>
+        <v>127697311</v>
       </c>
       <c r="B22" t="n">
         <v>79032</v>
@@ -2884,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480997</v>
+        <v>481070</v>
       </c>
       <c r="R22" t="n">
-        <v>6791673</v>
+        <v>6791717</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2919,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2929,7 +2934,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127698539</v>
+        <v>127698355</v>
       </c>
       <c r="B24" t="n">
-        <v>5177</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,42 +3084,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480934</v>
+        <v>480971</v>
       </c>
       <c r="R24" t="n">
-        <v>6791623</v>
+        <v>6791584</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,65 +3168,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127701326</v>
+        <v>127697861</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>78791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481100</v>
+        <v>481020</v>
       </c>
       <c r="R25" t="n">
-        <v>6791578</v>
+        <v>6791693</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3255,7 +3250,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3265,7 +3260,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3292,7 +3287,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127698896</v>
+        <v>127701320</v>
       </c>
       <c r="B26" t="n">
         <v>79064</v>
@@ -3327,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480939</v>
+        <v>481015</v>
       </c>
       <c r="R26" t="n">
-        <v>6791551</v>
+        <v>6791581</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,22 +3387,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127697861</v>
+        <v>127699426</v>
       </c>
       <c r="B27" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,37 +3410,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481020</v>
+        <v>481074</v>
       </c>
       <c r="R27" t="n">
-        <v>6791693</v>
+        <v>6791631</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3494,22 +3494,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127701320</v>
+        <v>127697758</v>
       </c>
       <c r="B28" t="n">
-        <v>79064</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3517,37 +3517,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481015</v>
+        <v>481047</v>
       </c>
       <c r="R28" t="n">
-        <v>6791581</v>
+        <v>6791700</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3586,12 +3586,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,60 +3601,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127699426</v>
+        <v>127701326</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481074</v>
+        <v>481100</v>
       </c>
       <c r="R29" t="n">
-        <v>6791631</v>
+        <v>6791578</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,22 +3713,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127697758</v>
+        <v>127698896</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3736,37 +3736,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481047</v>
+        <v>480939</v>
       </c>
       <c r="R30" t="n">
-        <v>6791700</v>
+        <v>6791551</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,12 +3820,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4707,53 +4707,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127698479</v>
+        <v>127698623</v>
       </c>
       <c r="B39" t="n">
-        <v>58350</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480971</v>
+        <v>480930</v>
       </c>
       <c r="R39" t="n">
-        <v>6791584</v>
+        <v>6791596</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4782,7 +4777,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4792,7 +4787,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4807,22 +4802,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127698924</v>
+        <v>127698475</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>58043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,39 +4825,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480949</v>
+        <v>480971</v>
       </c>
       <c r="R40" t="n">
-        <v>6791564</v>
+        <v>6791584</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4894,7 +4889,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4904,7 +4899,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4919,22 +4914,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127698230</v>
+        <v>127698924</v>
       </c>
       <c r="B41" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,21 +4937,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4971,13 +4966,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480934</v>
+        <v>480949</v>
       </c>
       <c r="R41" t="n">
-        <v>6791648</v>
+        <v>6791564</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5006,7 +5001,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5016,7 +5011,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5043,48 +5038,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127699014</v>
+        <v>127698230</v>
       </c>
       <c r="B42" t="n">
-        <v>78791</v>
+        <v>8439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481040</v>
+        <v>480934</v>
       </c>
       <c r="R42" t="n">
-        <v>6791597</v>
+        <v>6791648</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5138,22 +5138,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127700334</v>
+        <v>127700572</v>
       </c>
       <c r="B43" t="n">
-        <v>79621</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481204</v>
+        <v>481155</v>
       </c>
       <c r="R43" t="n">
-        <v>6791461</v>
+        <v>6791512</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5257,50 +5257,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127698475</v>
+        <v>127700793</v>
       </c>
       <c r="B44" t="n">
-        <v>58043</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480971</v>
+        <v>481102</v>
       </c>
       <c r="R44" t="n">
-        <v>6791584</v>
+        <v>6791567</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5332,7 +5327,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5342,7 +5337,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5369,48 +5364,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127700572</v>
+        <v>127701600</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>56864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481155</v>
+        <v>481051</v>
       </c>
       <c r="R45" t="n">
-        <v>6791512</v>
+        <v>6791546</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5439,7 +5434,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5449,7 +5444,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5464,57 +5464,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127700793</v>
+        <v>127698479</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>58350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481102</v>
+        <v>480971</v>
       </c>
       <c r="R46" t="n">
-        <v>6791567</v>
+        <v>6791584</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5546,7 +5551,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5556,7 +5561,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,10 +5588,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127698623</v>
+        <v>127699014</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5594,37 +5599,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480930</v>
+        <v>481040</v>
       </c>
       <c r="R47" t="n">
-        <v>6791596</v>
+        <v>6791597</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5653,7 +5658,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5663,7 +5668,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5678,60 +5683,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127701600</v>
+        <v>127700334</v>
       </c>
       <c r="B48" t="n">
-        <v>56864</v>
+        <v>79621</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481051</v>
+        <v>481204</v>
       </c>
       <c r="R48" t="n">
-        <v>6791546</v>
+        <v>6791461</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5760,7 +5765,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5770,12 +5775,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5790,12 +5790,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6678,53 +6678,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127699111</v>
+        <v>127700960</v>
       </c>
       <c r="B57" t="n">
-        <v>5197</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481041</v>
+        <v>481132</v>
       </c>
       <c r="R57" t="n">
-        <v>6791490</v>
+        <v>6791620</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6753,7 +6748,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6763,7 +6758,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6778,50 +6773,50 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127698670</v>
+        <v>127698582</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>57670</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6830,10 +6825,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480930</v>
+        <v>480934</v>
       </c>
       <c r="R58" t="n">
-        <v>6791596</v>
+        <v>6791623</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6902,10 +6897,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127697046</v>
+        <v>127696742</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>56864</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6913,27 +6908,36 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6942,13 +6946,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480998</v>
+        <v>480917</v>
       </c>
       <c r="R59" t="n">
-        <v>6791729</v>
+        <v>6791694</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6977,7 +6981,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6987,7 +6991,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7007,55 +7011,60 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127697093</v>
+        <v>127698994</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>56864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481044</v>
+        <v>480949</v>
       </c>
       <c r="R60" t="n">
-        <v>6791735</v>
+        <v>6791564</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7084,7 +7093,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7094,7 +7103,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7114,60 +7123,60 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127698582</v>
+        <v>127700902</v>
       </c>
       <c r="B61" t="n">
-        <v>57670</v>
+        <v>56864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480934</v>
+        <v>481153</v>
       </c>
       <c r="R61" t="n">
-        <v>6791623</v>
+        <v>6791594</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7196,7 +7205,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7206,7 +7215,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7221,60 +7230,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127700960</v>
+        <v>127699111</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>5197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481132</v>
+        <v>481041</v>
       </c>
       <c r="R62" t="n">
-        <v>6791620</v>
+        <v>6791490</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7303,7 +7317,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7313,7 +7327,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7328,50 +7342,50 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127699410</v>
+        <v>127698670</v>
       </c>
       <c r="B63" t="n">
-        <v>57673</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7380,13 +7394,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481141</v>
+        <v>480930</v>
       </c>
       <c r="R63" t="n">
-        <v>6791461</v>
+        <v>6791596</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7415,7 +7429,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7425,7 +7439,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7452,10 +7466,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127696742</v>
+        <v>127697046</v>
       </c>
       <c r="B64" t="n">
-        <v>56864</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7463,36 +7477,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7501,13 +7506,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480917</v>
+        <v>480998</v>
       </c>
       <c r="R64" t="n">
-        <v>6791694</v>
+        <v>6791729</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7536,7 +7541,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7546,7 +7551,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7566,60 +7571,55 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127698994</v>
+        <v>127697093</v>
       </c>
       <c r="B65" t="n">
-        <v>56864</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480949</v>
+        <v>481044</v>
       </c>
       <c r="R65" t="n">
-        <v>6791564</v>
+        <v>6791735</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7678,57 +7678,57 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127700902</v>
+        <v>127699410</v>
       </c>
       <c r="B66" t="n">
-        <v>56864</v>
+        <v>57673</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481153</v>
+        <v>481141</v>
       </c>
       <c r="R66" t="n">
-        <v>6791594</v>
+        <v>6791461</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7785,12 +7785,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127700455</v>
+        <v>127699309</v>
       </c>
       <c r="B82" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9463,21 +9463,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481162</v>
+        <v>481074</v>
       </c>
       <c r="R82" t="n">
-        <v>6791491</v>
+        <v>6791631</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9559,10 +9559,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127700497</v>
+        <v>127699161</v>
       </c>
       <c r="B83" t="n">
-        <v>75156</v>
+        <v>79621</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9570,37 +9570,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481155</v>
+        <v>480980</v>
       </c>
       <c r="R83" t="n">
-        <v>6791512</v>
+        <v>6791570</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9654,57 +9654,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127700910</v>
+        <v>127700777</v>
       </c>
       <c r="B84" t="n">
-        <v>92650</v>
+        <v>79621</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481139</v>
+        <v>481102</v>
       </c>
       <c r="R84" t="n">
-        <v>6791575</v>
+        <v>6791567</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9761,19 +9761,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127696956</v>
+        <v>127700455</v>
       </c>
       <c r="B85" t="n">
         <v>79032</v>
@@ -9804,17 +9804,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480973</v>
+        <v>481162</v>
       </c>
       <c r="R85" t="n">
-        <v>6791733</v>
+        <v>6791491</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9868,22 +9868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127699017</v>
+        <v>127700497</v>
       </c>
       <c r="B86" t="n">
-        <v>79032</v>
+        <v>75156</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9891,34 +9891,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481001</v>
+        <v>481155</v>
       </c>
       <c r="R86" t="n">
-        <v>6791490</v>
+        <v>6791512</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9975,22 +9975,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127700823</v>
+        <v>127696956</v>
       </c>
       <c r="B87" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9998,42 +9998,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481147</v>
+        <v>480973</v>
       </c>
       <c r="R87" t="n">
-        <v>6791569</v>
+        <v>6791733</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10062,7 +10057,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10072,7 +10067,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10092,61 +10087,52 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700837</v>
+        <v>127699017</v>
       </c>
       <c r="B88" t="n">
-        <v>56864</v>
+        <v>79032</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481147</v>
+        <v>481001</v>
       </c>
       <c r="R88" t="n">
-        <v>6791569</v>
+        <v>6791490</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10178,7 +10164,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10188,7 +10174,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10215,10 +10201,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127699309</v>
+        <v>127700823</v>
       </c>
       <c r="B89" t="n">
-        <v>78791</v>
+        <v>57670</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10226,37 +10212,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481074</v>
+        <v>481147</v>
       </c>
       <c r="R89" t="n">
-        <v>6791631</v>
+        <v>6791569</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10285,7 +10276,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10295,7 +10286,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10310,22 +10301,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127699161</v>
+        <v>127700371</v>
       </c>
       <c r="B90" t="n">
-        <v>79621</v>
+        <v>91360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10333,21 +10324,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10357,13 +10348,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>480980</v>
+        <v>481171</v>
       </c>
       <c r="R90" t="n">
-        <v>6791570</v>
+        <v>6791459</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10392,7 +10383,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10402,7 +10393,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10429,45 +10420,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127700777</v>
+        <v>127700910</v>
       </c>
       <c r="B91" t="n">
-        <v>79621</v>
+        <v>92650</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481102</v>
+        <v>481139</v>
       </c>
       <c r="R91" t="n">
-        <v>6791567</v>
+        <v>6791575</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10499,7 +10490,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10509,7 +10500,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10524,57 +10515,66 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127700371</v>
+        <v>127700837</v>
       </c>
       <c r="B92" t="n">
-        <v>91360</v>
+        <v>56864</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>481171</v>
+        <v>481147</v>
       </c>
       <c r="R92" t="n">
-        <v>6791459</v>
+        <v>6791569</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10862,45 +10862,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127698937</v>
+        <v>127699374</v>
       </c>
       <c r="B95" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>480949</v>
+        <v>481074</v>
       </c>
       <c r="R95" t="n">
-        <v>6791564</v>
+        <v>6791631</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10957,12 +10957,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11514,45 +11514,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127699374</v>
+        <v>127698937</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>481074</v>
+        <v>480949</v>
       </c>
       <c r="R101" t="n">
-        <v>6791631</v>
+        <v>6791564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11609,44 +11609,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127699081</v>
+        <v>127697411</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79621</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11656,13 +11656,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>480958</v>
+        <v>481081</v>
       </c>
       <c r="R102" t="n">
-        <v>6791568</v>
+        <v>6791711</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11701,7 +11701,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På roten av en gammal tallåga</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11716,60 +11721,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127701548</v>
+        <v>127696781</v>
       </c>
       <c r="B103" t="n">
-        <v>91325</v>
+        <v>79032</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>481100</v>
+        <v>480929</v>
       </c>
       <c r="R103" t="n">
-        <v>6791578</v>
+        <v>6791702</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11798,7 +11803,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11808,7 +11813,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11823,66 +11828,57 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127699358</v>
+        <v>127701548</v>
       </c>
       <c r="B104" t="n">
-        <v>91621</v>
+        <v>91325</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>65</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>481124</v>
+        <v>481100</v>
       </c>
       <c r="R104" t="n">
-        <v>6791490</v>
+        <v>6791578</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11914,7 +11910,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11924,12 +11920,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Bara en liten bit, men sannolikt denna art</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11956,48 +11947,57 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127697059</v>
+        <v>127699358</v>
       </c>
       <c r="B105" t="n">
-        <v>79064</v>
+        <v>91621</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>65</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>480998</v>
+        <v>481124</v>
       </c>
       <c r="R105" t="n">
-        <v>6791729</v>
+        <v>6791490</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12036,7 +12036,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Bara en liten bit, men sannolikt denna art</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12056,17 +12061,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127696781</v>
+        <v>127697059</v>
       </c>
       <c r="B106" t="n">
-        <v>79032</v>
+        <v>79064</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12074,37 +12079,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>480929</v>
+        <v>480998</v>
       </c>
       <c r="R106" t="n">
-        <v>6791702</v>
+        <v>6791729</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12133,7 +12138,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12143,7 +12148,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12158,12 +12163,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12282,32 +12287,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127697411</v>
+        <v>127699081</v>
       </c>
       <c r="B108" t="n">
-        <v>79621</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12317,13 +12322,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>481081</v>
+        <v>480958</v>
       </c>
       <c r="R108" t="n">
-        <v>6791711</v>
+        <v>6791568</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12352,7 +12357,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12362,12 +12367,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På roten av en gammal tallåga</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12382,22 +12382,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127698632</v>
+        <v>127696731</v>
       </c>
       <c r="B109" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12405,42 +12405,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>480963</v>
+        <v>480916</v>
       </c>
       <c r="R109" t="n">
-        <v>6791579</v>
+        <v>6791696</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12469,7 +12464,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12479,7 +12474,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12494,22 +12489,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127698465</v>
+        <v>127698632</v>
       </c>
       <c r="B110" t="n">
-        <v>57833</v>
+        <v>57673</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12517,42 +12512,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>480971</v>
+        <v>480963</v>
       </c>
       <c r="R110" t="n">
-        <v>6791584</v>
+        <v>6791579</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12581,7 +12576,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12591,7 +12586,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12606,22 +12601,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127698216</v>
+        <v>127698465</v>
       </c>
       <c r="B111" t="n">
-        <v>79032</v>
+        <v>57833</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12629,37 +12624,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>480972</v>
+        <v>480971</v>
       </c>
       <c r="R111" t="n">
-        <v>6791653</v>
+        <v>6791584</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12713,60 +12713,60 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127696731</v>
+        <v>127698322</v>
       </c>
       <c r="B112" t="n">
-        <v>79032</v>
+        <v>5197</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>480916</v>
+        <v>480936</v>
       </c>
       <c r="R112" t="n">
-        <v>6791696</v>
+        <v>6791610</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12820,44 +12820,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127698322</v>
+        <v>127698216</v>
       </c>
       <c r="B113" t="n">
-        <v>5197</v>
+        <v>79032</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12867,10 +12867,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480936</v>
+        <v>480972</v>
       </c>
       <c r="R113" t="n">
-        <v>6791610</v>
+        <v>6791653</v>
       </c>
       <c r="S113" t="n">
         <v>9</v>
@@ -15010,7 +15010,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127697242</v>
+        <v>127699578</v>
       </c>
       <c r="B133" t="n">
         <v>79032</v>
@@ -15045,13 +15045,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>481040</v>
+        <v>481202</v>
       </c>
       <c r="R133" t="n">
-        <v>6791735</v>
+        <v>6791440</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15110,14 +15110,14 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127699578</v>
+        <v>127697242</v>
       </c>
       <c r="B134" t="n">
         <v>79032</v>
@@ -15152,13 +15152,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>481202</v>
+        <v>481040</v>
       </c>
       <c r="R134" t="n">
-        <v>6791440</v>
+        <v>6791735</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Håkan Thenander, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -18941,7 +18941,7 @@
         <v>127698825</v>
       </c>
       <c r="B169" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -18941,7 +18941,7 @@
         <v>127698825</v>
       </c>
       <c r="B169" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>

--- a/artfynd/A 36188-2025 artfynd.xlsx
+++ b/artfynd/A 36188-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY173"/>
+  <dimension ref="A1:AZ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696761</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697059</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697134</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697194</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698193</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698461</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698631</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698896</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698916</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701320</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2092,6 +2157,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702694</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2198,6 +2268,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702710</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2304,6 +2379,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702746</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2411,6 +2491,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698467</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2518,6 +2603,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698294</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2625,6 +2715,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696659</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2732,6 +2827,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696731</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2839,6 +2939,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696763</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2946,6 +3051,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696785</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3053,6 +3163,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696868</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3160,6 +3275,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696895</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3267,6 +3387,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696956</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3374,6 +3499,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696982</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3486,6 +3616,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697027</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3593,6 +3728,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697069</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3700,6 +3840,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697100</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3807,6 +3952,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697101</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3914,6 +4064,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697135</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4021,6 +4176,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697174</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4128,6 +4288,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697258</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4235,6 +4400,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697947</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4342,6 +4512,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698037</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4449,6 +4624,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698134</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4556,6 +4736,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698172</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4668,6 +4853,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698242</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4775,6 +4965,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698283</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4882,6 +5077,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698383</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4994,6 +5194,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698427</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5101,6 +5306,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698623</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5208,6 +5418,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698625</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5315,6 +5530,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698677</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5422,6 +5642,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698695</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5529,6 +5754,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698773</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5636,6 +5866,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698861</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5743,6 +5978,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698999</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5850,6 +6090,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699017</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5957,6 +6202,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699069</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6064,6 +6314,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699151</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6171,6 +6426,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697142</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6278,6 +6538,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697277</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6390,6 +6655,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698286</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6502,6 +6772,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698346</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6614,6 +6889,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698582</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6726,6 +7006,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699200</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6838,6 +7123,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698040</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6950,6 +7240,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698278</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7062,6 +7357,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698374</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7174,6 +7474,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698619</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7286,6 +7591,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698632</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7398,6 +7708,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698978</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7510,6 +7825,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699090</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7622,6 +7942,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796538</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7743,6 +8068,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696742</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7860,6 +8190,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697024</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7972,6 +8307,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697901</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8084,6 +8424,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698878</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8196,6 +8541,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698994</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8308,6 +8658,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698996</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8420,6 +8775,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796617</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8532,6 +8892,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698539</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8644,6 +9009,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698857</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8756,6 +9126,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699033</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8868,6 +9243,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699095</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8980,6 +9360,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699166</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9092,6 +9477,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697874</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9204,6 +9594,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698475</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9316,6 +9711,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698465</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9432,6 +9832,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698885</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9544,6 +9949,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699075</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9656,6 +10066,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698479</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9763,6 +10178,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698322</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9875,6 +10295,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697046</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9987,6 +10412,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698347</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10094,6 +10524,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698355</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10206,6 +10641,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698670</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10318,6 +10758,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698924</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10425,6 +10870,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699081</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10537,6 +10987,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699193</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10649,6 +11104,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698230</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10756,6 +11216,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697861</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10863,6 +11328,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698243</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10970,6 +11440,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698937</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11077,6 +11552,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699145</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11184,6 +11664,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697865</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11291,6 +11776,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699161</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11402,6 +11892,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127698825</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11523,6 +12018,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699358</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11635,6 +12135,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696978</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11742,6 +12247,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697430</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11854,6 +12364,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697912</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11966,6 +12481,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700382</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12073,6 +12593,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700636</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12185,6 +12710,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701082</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12296,6 +12826,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699163</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12403,6 +12938,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700371</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12510,6 +13050,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796449</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12617,6 +13162,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701084</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12724,6 +13274,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700910</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12831,6 +13386,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697402</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12938,6 +13498,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700590</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13045,6 +13610,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697245</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13152,6 +13722,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701548</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13259,6 +13834,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697093</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13366,6 +13946,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697242</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13473,6 +14058,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697256</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13580,6 +14170,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697328</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13687,6 +14282,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697465</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13799,6 +14399,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697831</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13906,6 +14511,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699026</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14013,6 +14623,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699348</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14120,6 +14735,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699444</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14227,6 +14847,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699478</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14334,6 +14959,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699578</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14441,6 +15071,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700359</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14548,6 +15183,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700440</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14655,6 +15295,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700455</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14762,6 +15407,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700494</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14869,6 +15519,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700714</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14976,6 +15631,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700745</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15083,6 +15743,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700960</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15190,6 +15855,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701141</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15302,6 +15972,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701374</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15418,6 +16093,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701839</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15519,6 +16199,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127801885</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15626,6 +16311,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700497</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15733,6 +16423,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699307</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15845,6 +16540,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699269</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15957,6 +16657,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699527</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16069,6 +16774,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700823</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16181,6 +16891,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701188</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16293,6 +17008,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697267</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16400,6 +17120,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697365</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16512,6 +17237,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697743</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16624,6 +17354,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699410</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16736,6 +17471,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701512</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16848,6 +17588,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127794167</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16960,6 +17705,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697747</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17076,6 +17826,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700837</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17188,6 +17943,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700902</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17300,6 +18060,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701600</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17412,6 +18177,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699098</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17524,6 +18294,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699221</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17636,6 +18411,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701326</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17748,6 +18528,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699111</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17860,6 +18645,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127701318</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17972,6 +18762,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699211</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18079,6 +18874,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699374</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18191,6 +18991,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699393</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18298,6 +19103,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699451</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18410,6 +19220,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700751</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18517,6 +19332,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700845</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18624,6 +19444,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699014</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18731,6 +19556,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699309</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18837,6 +19667,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127714349</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18949,6 +19784,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127697411</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19056,6 +19896,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699004</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19163,6 +20008,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127699297</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19270,6 +20120,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700334</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19377,6 +20232,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700777</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19489,8 +20349,187 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127696912</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>